--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="produtcs" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="produtcs" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="products" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>images</t>
+  </si>
+  <si>
+    <t>inStock</t>
+  </si>
+  <si>
+    <t>madeToOrder</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>sizes</t>
+  </si>
+  <si>
+    <t>createdAt</t>
+  </si>
   <si>
     <t>Футболка Dior</t>
   </si>
@@ -22,7 +61,7 @@
     <t>12000</t>
   </si>
   <si>
-    <t>RUB</t>
+    <t>₽</t>
   </si>
   <si>
     <t>Материал хлопок</t>
@@ -221,7 +260,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -232,6 +271,21 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFE4E4E4"/>
+      <name val="Menlo"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFE4E4E4"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -246,26 +300,49 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -486,926 +563,967 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1">
-        <v>1.0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+        <v>49</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>66</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
+        <v>71</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
         <v>20.0</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="E21" s="3"/>
+      <c r="B21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="22">
-      <c r="E22" s="3"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23">
-      <c r="E23" s="3"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24">
-      <c r="E24" s="3"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25">
-      <c r="E25" s="3"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26">
-      <c r="E26" s="3"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27">
-      <c r="E27" s="3"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28">
-      <c r="E28" s="3"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29">
-      <c r="E29" s="3"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30">
-      <c r="E30" s="3"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31">
-      <c r="E31" s="3"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32">
-      <c r="E32" s="3"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33">
-      <c r="E33" s="3"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34">
-      <c r="E34" s="3"/>
+      <c r="E34" s="7"/>
     </row>
     <row r="35">
-      <c r="E35" s="3"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36">
-      <c r="E36" s="3"/>
+      <c r="E36" s="7"/>
     </row>
     <row r="37">
-      <c r="E37" s="3"/>
+      <c r="E37" s="7"/>
     </row>
     <row r="38">
-      <c r="E38" s="3"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39">
-      <c r="E39" s="3"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40">
-      <c r="E40" s="3"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41">
-      <c r="E41" s="3"/>
+      <c r="E41" s="7"/>
     </row>
     <row r="42">
-      <c r="E42" s="3"/>
+      <c r="E42" s="7"/>
     </row>
     <row r="43">
-      <c r="E43" s="3"/>
+      <c r="E43" s="7"/>
     </row>
     <row r="44">
-      <c r="E44" s="3"/>
+      <c r="E44" s="7"/>
     </row>
     <row r="45">
-      <c r="E45" s="3"/>
+      <c r="E45" s="7"/>
     </row>
     <row r="46">
-      <c r="E46" s="3"/>
+      <c r="E46" s="7"/>
     </row>
     <row r="47">
-      <c r="E47" s="3"/>
+      <c r="E47" s="7"/>
     </row>
     <row r="48">
-      <c r="E48" s="3"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49">
-      <c r="E49" s="3"/>
+      <c r="E49" s="7"/>
     </row>
     <row r="50">
-      <c r="E50" s="3"/>
+      <c r="E50" s="7"/>
     </row>
     <row r="51">
-      <c r="E51" s="3"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H1"/>
-    <hyperlink r:id="rId2" ref="H2"/>
-    <hyperlink r:id="rId3" ref="H3"/>
-    <hyperlink r:id="rId4" ref="H5"/>
-    <hyperlink r:id="rId5" ref="H16"/>
-    <hyperlink r:id="rId6" ref="H19"/>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="H4"/>
+    <hyperlink r:id="rId4" ref="H6"/>
+    <hyperlink r:id="rId5" ref="H17"/>
+    <hyperlink r:id="rId6" ref="H20"/>
   </hyperlinks>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433046AA-9CD3-F148-A12D-67645EE98721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="products" sheetId="1" r:id="rId5"/>
+    <sheet name="products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="182">
   <si>
     <t>id</t>
   </si>
@@ -254,42 +263,381 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657434/tg-products/petjj0v2jgsvjhxu2t2y.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657436/tg-products/glwgfyzvoxrivzb8bvrc.jpg</t>
+  </si>
+  <si>
+    <t>Cумка Bottega Veneta</t>
+  </si>
+  <si>
+    <t>Bottega Veneta</t>
+  </si>
+  <si>
+    <t>Материал кожа</t>
+  </si>
+  <si>
+    <t>bags</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816112/tg-products/pitfg5ru3uln0ddtof3r.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816115/tg-products/lxtt0igpkxfq0wsizh7i.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816337/tg-products/phyafi9uw9fmj6bc1ci7.jpg</t>
+  </si>
+  <si>
+    <t>зеленый</t>
+  </si>
+  <si>
+    <t>25х19 см</t>
+  </si>
+  <si>
+    <t>Ветровка YSL</t>
+  </si>
+  <si>
+    <t>YSL</t>
+  </si>
+  <si>
+    <t>Материал нейлон</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816339/tg-products/fsfrtxbtdfo0s02zgsmd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816341/tg-products/jn9iloy9lyux1gyegmxx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816513/tg-products/pakoq54nopsn1hndpde9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816516/tg-products/ayxvxbmsubumkq11iab2.jpg</t>
+  </si>
+  <si>
+    <t>Поло Miumiu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816519/tg-products/ohoa6wyjmwem3mpabu2y.jpg</t>
+  </si>
+  <si>
+    <t>Лонгслив Celine</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816630/tg-products/rzhuphpv934hsspwjcac.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816632/tg-products/wcczjq0eafp70qnq7yxb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816635/tg-products/y8abqxdgeqradf9v8kn3.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816898/tg-products/wc9dbqqabjssntstope5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816901/tg-products/nqgnpv4nhjbwiu7hjvtq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816903/tg-products/di8f3jkcpgga3r9qmcyb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817251/tg-products/i734pcf89hwihtvndvkd.jpg</t>
+  </si>
+  <si>
+    <t>Юбка Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817254/tg-products/rizqedb0kzzpw8mad3b6.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817256/tg-products/d1fiiqkepfx7wueogmvt.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817313/tg-products/b7eg1yovz5ynm5blftej.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817315/tg-products/vcl3bibo013ehsgxzfpm.jpg</t>
+  </si>
+  <si>
+    <t>Джинсы Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>Материал Хлопок</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817318/tg-products/ylgzcd8hw89ryxuy9wgb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817502/tg-products/yxbdwftwbt2nwhpdltis.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817505/tg-products/dbfkikayeksfittpg3c3.jpg</t>
+  </si>
+  <si>
+    <t>Рубашка Valentino</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817508/tg-products/w1svjywfln1pih49hg8t.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817642/tg-products/lmdkaqnxyh5f14hohww3.jpg</t>
+  </si>
+  <si>
+    <t>Майка Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817645/tg-products/jnynyokfyhj3qsyx9xnj.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817647/tg-products/bfrmyir175yqnr9ob40p.jpg</t>
+  </si>
+  <si>
+    <t>черный</t>
+  </si>
+  <si>
+    <t>Рубашка Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817754/tg-products/cpfreiffmhgyzd93datj.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817756/tg-products/sf2k3vztxn4ic512gzsx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817758/tg-products/jh8oydbviq4dukpfcnu8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817777/tg-products/db51stpkjb9qyt1xf4oa.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817780/tg-products/riy5n5zhqnbwt4pmjth6.jpg</t>
+  </si>
+  <si>
+    <t>коричневый</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817782/tg-products/ufiiywegloio1x0gqdup.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830691/tg-products/dhjldil5xwzxwdvvsy4d.jpg</t>
+  </si>
+  <si>
+    <t>Кроссовки Hermes</t>
+  </si>
+  <si>
+    <t>Hermes</t>
+  </si>
+  <si>
+    <t>shoes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830697/tg-products/t58uzuebmuahcobfnwve.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830700/tg-products/rodsy5dk3l0a8xiqcril.jpg</t>
+  </si>
+  <si>
+    <t>35 36 37 38 39 40</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830715/tg-products/quangmttkambhc1znxav.jpg</t>
+  </si>
+  <si>
+    <t>35 36 37 38 39 40 41</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773831036/tg-products/unwdetsib4dlzmfdv48s.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773831046/tg-products/grimurzletjsua1gmqk1.jpg</t>
+  </si>
+  <si>
+    <t>желтый</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773831079/tg-products/jloj0hbjgwekrutieahz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773831089/tg-products/hxkhhhip0ijqt5v5q2mx.jpg</t>
+  </si>
+  <si>
+    <t>Сандали Hermes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832274/tg-products/g6hhw3jzcfj9zpmhubw4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832280/tg-products/feqhnyy71cywneo2dgpl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832369/tg-products/aldnd72iz8d5gxonmpru.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832380/tg-products/nfwisjjlygrbiwvqrlnj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832393/tg-products/tsrxehwaflauewsewans.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832415/tg-products/vqgvx5kif1xfzsda0sgk.jpg</t>
+  </si>
+  <si>
+    <t>Сапоги Hermes</t>
+  </si>
+  <si>
+    <t>Материал замша</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832469/tg-products/c3uwat07b6hj2gwxeieo.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832489/tg-products/hoyxfa8ipfzqlzqak997.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832537/tg-products/t0e2rduxmfdir1orp8pj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832550/tg-products/epnyi36al38fmhgtjvly.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832563/tg-products/ubk1xzznnsu2wdhbqxml.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832870/tg-products/phxbyatfhjuwt6vmlvwo.jpg</t>
+  </si>
+  <si>
+    <t>S M L XL</t>
+  </si>
+  <si>
+    <t>Куртка Miumiu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832887/tg-products/ittb2gs68rdf0mj2jxli.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832909/tg-products/xilvbbhlgzrhqzmi6aax.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Bottega Veneta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832951/tg-products/oqyrr4f8dkvu1tbfp9pn.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Loewe</t>
+  </si>
+  <si>
+    <t>Loewe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832970/tg-products/aeoeqtxt2jaikgzifwta.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773832980/tg-products/itzlzjtttic6kpfo9u6k.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Ralph Lauren</t>
+  </si>
+  <si>
+    <t>Ralph Lauren</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833016/tg-products/jeoxdlgvx885ilu5ppjy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833036/tg-products/fwfq56v1fhvye5vn7tca.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833663/tg-products/dqdejnonpwlysoyuulm5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833667/tg-products/ajna4isso0n29hf2pece.jpg</t>
+  </si>
+  <si>
+    <t>Сумка Bottega Veneta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833670/tg-products/hwxadkpms9jh21fxw3jy.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833745/tg-products/p55aadptaigq65lca5gw.jpg</t>
+  </si>
+  <si>
+    <t>39x25x18.5 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833753/tg-products/n1h2jljzzvnvbb5vuqm9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833757/tg-products/hlit3tg9hcvolmikvqj8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833786/tg-products/itgmxlmrxnmqpluutqyg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833789/tg-products/hjhf0t97cpv5ikiaachr.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833792/tg-products/i43cheic3jgchzlrutej.jpg</t>
+  </si>
+  <si>
+    <t>бордовый</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833835/tg-products/ybmj3n0lwzafivnpl1uw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833838/tg-products/js8z3k0d0dfxtckeecxz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833841/tg-products/ie7ieg44kpg7mqziwb5l.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833909/tg-products/k4pbk87mhwndsrpoz0js.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833913/tg-products/to7x83ks9mydmb4zwzfs.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833917/tg-products/a0zubiodyon2xd1rfik2.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833932/tg-products/fy8m8n6xt24oowu69bdl.jpg</t>
+  </si>
+  <si>
+    <t>красный</t>
+  </si>
+  <si>
+    <t>21x11x9 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833936/tg-products/kf5evug3y3afwlfsxe7k.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833938/tg-products/uqpacz5ywnypbmulzpad.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833962/tg-products/vxgzb3plkv0lljydi0ql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833965/tg-products/wsn7tqksvlrvoj5odctx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833969/tg-products/pboh9oo8jcgcnpj5bytv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834028/tg-products/dll5ilxr2cvrfrmb5zr6.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834031/tg-products/tjayysex8bzeuofpthiq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834035/tg-products/isuda1chzxqhf49cazlb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834086/tg-products/q4zbjv25kvxpeiurtwb7.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834089/tg-products/ah9ybpq58ps4c5cw1gsc.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834092/tg-products/uy6cqzf4y0uro9otz8hf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834321/tg-products/k4bkfhn2f10ssvrtgm5u.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834325/tg-products/z3olimdqvrbbchauxyp8.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835308/tg-products/zyxgjrvtjv4ea5yd2whz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835311/tg-products/nj42wapveufuq94tux7b.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835315/tg-products/ingo8tua2bmu4cjt7m9b.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835498/tg-products/ixvsxn6ng5h39sv1jhkl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835503/tg-products/uyhrzy2a1xgzdlghyspy.jpg</t>
+  </si>
+  <si>
+    <t>17x10x6 см</t>
+  </si>
+  <si>
+    <t>Костюм Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>Материал хлопок и лен</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835510/tg-products/aebnsybv0vx8mlu8c3pq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835518/tg-products/yjwfs60rgbkm5sdc0mvj.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835528/tg-products/kx4c8ffj2yggtj92tszv.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835561/tg-products/djmln37ynprbvnw9j3kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835567/tg-products/bcloy4laepu7xjnximux.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835577/tg-products/ms4qzopjvfmnvxe4fyql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835610/tg-products/ry6zindmjsnornscgrre.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835614/tg-products/maa475djsqbflpsu43uq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835617/tg-products/xfa7pbpame6l5jhjcy2r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835759/tg-products/iwhcisnvkwzcfly0mlih.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835767/tg-products/btetnlvzi7jaytlrij2j.jpg</t>
+  </si>
+  <si>
+    <t>Пиджак Loro Piana</t>
+  </si>
+  <si>
+    <t>Loro Piana</t>
+  </si>
+  <si>
+    <t>Материал шерсть</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835773/tg-products/eokilkgoajhxjgjaknxs.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835778/tg-products/auyz4azjhufbybxeoccy.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.0"/>
-      <color rgb="FFE4E4E4"/>
-      <name val="Menlo"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFE4E4E4"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="3"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -297,11 +645,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF9A9A9A"/>
@@ -315,46 +669,42 @@
       <bottom style="thin">
         <color rgb="FF9A9A9A"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -362,7 +712,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -552,60 +902,63 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M145"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -613,10 +966,10 @@
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -625,13 +978,13 @@
       <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -640,13 +993,13 @@
       <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -654,10 +1007,10 @@
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -666,13 +1019,13 @@
       <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -681,13 +1034,13 @@
       <c r="L3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>27</v>
@@ -695,10 +1048,10 @@
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -707,13 +1060,13 @@
       <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -722,13 +1075,13 @@
       <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
@@ -736,10 +1089,10 @@
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -751,10 +1104,10 @@
       <c r="H5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -763,13 +1116,13 @@
       <c r="L5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>32</v>
@@ -777,10 +1130,10 @@
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -789,13 +1142,13 @@
       <c r="G6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -804,13 +1157,13 @@
       <c r="L6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>37</v>
@@ -818,10 +1171,10 @@
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -833,10 +1186,10 @@
       <c r="H7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -845,13 +1198,13 @@
       <c r="L7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>41</v>
@@ -859,10 +1212,10 @@
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -874,10 +1227,10 @@
       <c r="H8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="I8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -886,13 +1239,13 @@
       <c r="L8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>41</v>
@@ -900,10 +1253,10 @@
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -915,10 +1268,10 @@
       <c r="H9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -927,13 +1280,13 @@
       <c r="L9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>48</v>
@@ -941,10 +1294,10 @@
       <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -956,10 +1309,10 @@
       <c r="H10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="I10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -968,13 +1321,13 @@
       <c r="L10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>52</v>
@@ -982,10 +1335,10 @@
       <c r="C11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -997,10 +1350,10 @@
       <c r="H11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -1009,13 +1362,13 @@
       <c r="L11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
@@ -1023,10 +1376,10 @@
       <c r="C12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1038,10 +1391,10 @@
       <c r="H12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -1050,13 +1403,13 @@
       <c r="L12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>61</v>
@@ -1064,10 +1417,10 @@
       <c r="C13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1079,10 +1432,10 @@
       <c r="H13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="I13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -1091,13 +1444,13 @@
       <c r="L13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>63</v>
@@ -1105,10 +1458,10 @@
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1120,10 +1473,10 @@
       <c r="H14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -1132,13 +1485,13 @@
       <c r="L14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>41</v>
@@ -1146,10 +1499,10 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1161,10 +1514,10 @@
       <c r="H15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="I15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -1173,13 +1526,13 @@
       <c r="L15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>67</v>
@@ -1187,10 +1540,10 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1202,10 +1555,10 @@
       <c r="H16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="I16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1214,13 +1567,13 @@
       <c r="L16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>70</v>
@@ -1228,10 +1581,10 @@
       <c r="C17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1240,13 +1593,13 @@
       <c r="G17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="I17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1255,13 +1608,13 @@
       <c r="L17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>73</v>
@@ -1269,10 +1622,10 @@
       <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1284,10 +1637,10 @@
       <c r="H18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="I18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -1296,13 +1649,13 @@
       <c r="L18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>52</v>
@@ -1310,10 +1663,10 @@
       <c r="C19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -1325,10 +1678,10 @@
       <c r="H19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="I19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -1337,13 +1690,13 @@
       <c r="L19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="M19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -1351,10 +1704,10 @@
       <c r="C20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -1363,13 +1716,13 @@
       <c r="G20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="I20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -1378,13 +1731,13 @@
       <c r="L20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>79</v>
@@ -1392,10 +1745,10 @@
       <c r="C21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1407,10 +1760,10 @@
       <c r="H21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="I21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -1419,112 +1772,3185 @@
       <c r="L21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23">
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24">
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25">
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26">
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28">
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29">
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31">
-      <c r="E31" s="7"/>
-    </row>
-    <row r="32">
-      <c r="E32" s="7"/>
-    </row>
-    <row r="33">
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34">
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35">
-      <c r="E35" s="7"/>
-    </row>
-    <row r="36">
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="E42" s="7"/>
-    </row>
-    <row r="43">
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44">
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45">
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46">
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47">
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48">
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49">
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50">
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51">
-      <c r="E51" s="7"/>
-    </row>
-    <row r="52">
-      <c r="E52" s="7"/>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="8">
+        <v>52000</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="8">
+        <v>39000</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="8">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="8">
+        <v>13000</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="8">
+        <v>13000</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="8">
+        <v>18000</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="8">
+        <v>28000</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M33" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M34" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M35" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M37" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M38" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M39" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M40" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M41" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M42" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M43" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M44" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="8">
+        <v>27000</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M45" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="8">
+        <v>27000</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M46" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M47" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M48" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M49" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M50" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M51" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M52" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="8">
+        <v>65000</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M53" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="8">
+        <v>60000</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M54" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="8">
+        <v>60000</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M55" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="8">
+        <v>60000</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M56" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M57" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" s="8">
+        <v>64000</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="M58" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="8">
+        <v>64000</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="M59" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="8">
+        <v>64000</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="M60" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="8">
+        <v>64000</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="M61" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M62" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M63" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M64" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M65" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M66" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M67" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M68" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="M69" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="8">
+        <v>63000</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M70" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M71" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="8">
+        <v>36000</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M72" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D73" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M73" s="10">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+    </row>
+    <row r="86" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+    </row>
+    <row r="87" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+    </row>
+    <row r="89" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+    </row>
+    <row r="90" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
+    </row>
+    <row r="91" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+    </row>
+    <row r="92" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
+    </row>
+    <row r="93" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+    </row>
+    <row r="94" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+    </row>
+    <row r="95" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+    </row>
+    <row r="96" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+    </row>
+    <row r="97" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+    </row>
+    <row r="98" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+    </row>
+    <row r="99" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+    </row>
+    <row r="100" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+    </row>
+    <row r="101" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+    </row>
+    <row r="102" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+    </row>
+    <row r="103" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+    </row>
+    <row r="104" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="M104" s="8"/>
+    </row>
+    <row r="105" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+    </row>
+    <row r="106" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+    </row>
+    <row r="107" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
+    </row>
+    <row r="108" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+      <c r="M108" s="8"/>
+    </row>
+    <row r="109" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="M109" s="8"/>
+    </row>
+    <row r="110" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+      <c r="M110" s="8"/>
+    </row>
+    <row r="111" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
+    </row>
+    <row r="112" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+      <c r="M112" s="8"/>
+    </row>
+    <row r="113" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
+    </row>
+    <row r="114" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
+    </row>
+    <row r="115" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+    </row>
+    <row r="116" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
+    </row>
+    <row r="117" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
+    </row>
+    <row r="118" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+    </row>
+    <row r="119" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+      <c r="M119" s="8"/>
+    </row>
+    <row r="120" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="8"/>
+    </row>
+    <row r="121" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+    </row>
+    <row r="122" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="8"/>
+      <c r="L122" s="8"/>
+      <c r="M122" s="8"/>
+    </row>
+    <row r="123" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+    </row>
+    <row r="124" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="8"/>
+      <c r="L124" s="8"/>
+      <c r="M124" s="8"/>
+    </row>
+    <row r="125" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+    </row>
+    <row r="126" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
+    </row>
+    <row r="127" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+    </row>
+    <row r="128" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="8"/>
+      <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
+    </row>
+    <row r="129" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="8"/>
+      <c r="F129" s="8"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="8"/>
+      <c r="L129" s="8"/>
+      <c r="M129" s="8"/>
+    </row>
+    <row r="130" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+    </row>
+    <row r="131" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
+    </row>
+    <row r="132" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
+    </row>
+    <row r="133" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="8"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
+    </row>
+    <row r="134" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="8"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="8"/>
+      <c r="L134" s="8"/>
+      <c r="M134" s="8"/>
+    </row>
+    <row r="135" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="8"/>
+      <c r="M135" s="8"/>
+    </row>
+    <row r="136" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+      <c r="M136" s="8"/>
+    </row>
+    <row r="137" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
+    </row>
+    <row r="138" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="8"/>
+      <c r="L138" s="8"/>
+      <c r="M138" s="8"/>
+    </row>
+    <row r="139" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="8"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="8"/>
+      <c r="L139" s="8"/>
+      <c r="M139" s="8"/>
+    </row>
+    <row r="140" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
+    </row>
+    <row r="141" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="8"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="8"/>
+      <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
+    </row>
+    <row r="142" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="8"/>
+      <c r="M142" s="8"/>
+    </row>
+    <row r="143" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="8"/>
+      <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
+    </row>
+    <row r="144" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="8"/>
+      <c r="L144" s="8"/>
+      <c r="M144" s="8"/>
+    </row>
+    <row r="145" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8"/>
+      <c r="K145" s="8"/>
+      <c r="L145" s="8"/>
+      <c r="M145" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="H3"/>
-    <hyperlink r:id="rId3" ref="H4"/>
-    <hyperlink r:id="rId4" ref="H6"/>
-    <hyperlink r:id="rId5" ref="H17"/>
-    <hyperlink r:id="rId6" ref="H20"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="H17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="H20" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="H24" r:id="rId7" xr:uid="{A012D9DA-3D0B-8E4F-81C4-E72240D32D91}"/>
+    <hyperlink ref="H34" r:id="rId8" xr:uid="{CBF69593-0295-B946-B89A-647666E9F901}"/>
+    <hyperlink ref="H35" r:id="rId9" xr:uid="{8B1CB10F-5634-424D-A0F7-5C3E436319B0}"/>
+    <hyperlink ref="H36" r:id="rId10" xr:uid="{B3141A86-4A15-A34D-9D04-D92B792D66F1}"/>
+    <hyperlink ref="H37" r:id="rId11" xr:uid="{2959309C-A9B0-BA4B-8EA9-728CBD66E2FA}"/>
+    <hyperlink ref="H38" r:id="rId12" xr:uid="{275A3BFA-F9E1-0E4A-8420-B7C62D47B7A9}"/>
+    <hyperlink ref="H39" r:id="rId13" xr:uid="{2606A1BF-0069-EC40-8A42-492EE88C90C7}"/>
+    <hyperlink ref="H40" r:id="rId14" xr:uid="{7C0EA247-23DC-5744-8C62-1FB4CA7E5F99}"/>
+    <hyperlink ref="H41" r:id="rId15" xr:uid="{E02425ED-2DE1-4647-A30F-8711F1865BDA}"/>
+    <hyperlink ref="H42" r:id="rId16" xr:uid="{538AAD2D-FE9C-4144-843E-8EC1DA5D39A4}"/>
+    <hyperlink ref="H43" r:id="rId17" xr:uid="{04CC1DE1-F266-1946-A15C-FB83ED202483}"/>
+    <hyperlink ref="H44" r:id="rId18" xr:uid="{2170793E-46BF-E447-B0CF-ED46B27717D3}"/>
+    <hyperlink ref="H45" r:id="rId19" xr:uid="{B9A6B017-B19C-B443-820F-7B894F55E934}"/>
+    <hyperlink ref="H46" r:id="rId20" xr:uid="{7184DB47-BA31-934A-8106-1EA0B41AFF11}"/>
+    <hyperlink ref="H47" r:id="rId21" xr:uid="{843AD2F3-6756-4F41-BC7D-86E7CC8DC447}"/>
+    <hyperlink ref="H48" r:id="rId22" xr:uid="{608AA630-C131-914A-BEE8-C4673E1407A8}"/>
+    <hyperlink ref="H49" r:id="rId23" xr:uid="{617DCBF8-FA99-824B-8396-5A5389E45137}"/>
+    <hyperlink ref="H50" r:id="rId24" xr:uid="{C4944DBB-27FF-754D-84B3-3BB97AE35ECE}"/>
+    <hyperlink ref="H51" r:id="rId25" xr:uid="{674B84DF-D7E3-3F49-BE14-2997C45FB26A}"/>
+    <hyperlink ref="H52" r:id="rId26" xr:uid="{7E6F0B0B-7CBB-8942-96F6-30A1C0A615CF}"/>
+    <hyperlink ref="H53" r:id="rId27" xr:uid="{A4D7A43D-BE11-634A-8DBD-78C7D796F803}"/>
+    <hyperlink ref="H54" r:id="rId28" xr:uid="{7233964D-8BFC-4549-B50D-7C87413CAAB7}"/>
+    <hyperlink ref="H55" r:id="rId29" xr:uid="{053E0B1B-E0FC-364D-92B4-30061EC2D209}"/>
+    <hyperlink ref="H56" r:id="rId30" xr:uid="{1D3BB45C-C7E9-174F-8F72-A00DC3563F84}"/>
+    <hyperlink ref="H67" r:id="rId31" xr:uid="{BCA705D2-FDC0-1C4D-8B19-E359DFC50FFF}"/>
+    <hyperlink ref="H68" r:id="rId32" xr:uid="{8E93EE4F-9052-A844-916D-D6F1C62AAF47}"/>
   </hyperlinks>
-  <drawing r:id="rId7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433046AA-9CD3-F148-A12D-67645EE98721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2D99DD-513E-7C48-BBEA-C430C895E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="185">
   <si>
     <t>id</t>
   </si>
@@ -112,9 +112,6 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773656988/tg-products/nd2ndp0l7e13lpno5hpb.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657069/tg-products/bhgxysknyx1l2jk9u3rn.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657073/tg-products/kwpdv0osksg4zvrudyr0.jpg</t>
-  </si>
-  <si>
     <t>розовый</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>Valentino</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657079/tg-products/z6chjwosq1tsmqmouhm6.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657082/tg-products/pw2oxr6l74zinnsgk6w0.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657085/tg-products/tjrhi6r2xvl4ygdssfrd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657088/tg-products/d7dqmbr96bs05rswdldf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657095/tg-products/thgk4m3rmewg5utuvs7v.jpg</t>
-  </si>
-  <si>
     <t>голбой</t>
   </si>
   <si>
@@ -151,9 +145,6 @@
     <t>24000</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657098/tg-products/rsyptz7fwqfelmxy6ydw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657100/tg-products/m9mzf7z9totbgmrwy7ly.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657147/tg-products/xncdhbxhflitmubbgm9a.jpg</t>
-  </si>
-  <si>
     <t>голубой</t>
   </si>
   <si>
@@ -163,9 +154,6 @@
     <t>Материал кашемир</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657152/tg-products/jdsaqx31zr7cjvimmbxg.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657154/tg-products/fnys55hvcsadqrlc19hf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657157/tg-products/bxyru9eahuawsrqxoquo.jpg</t>
-  </si>
-  <si>
     <t>Футболка Louis Vuitton</t>
   </si>
   <si>
@@ -175,9 +163,6 @@
     <t>14000</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657159/tg-products/ucwhnnndkjvjj0rfgch7.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657161/tg-products/rxt1h8ofjx9eqvv2sqqz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657164/tg-products/sswmebnlaxvoisvuawct.jpg</t>
-  </si>
-  <si>
     <t>Брюки Chanel</t>
   </si>
   <si>
@@ -190,9 +175,6 @@
     <t>Материал шелк и полиэстер</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657167/tg-products/j01zqhctwihp1juowjcy.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657170/tg-products/ev23h726ddf3tyt3rrae.jpg</t>
-  </si>
-  <si>
     <t>Рубашка Chanel</t>
   </si>
   <si>
@@ -202,36 +184,21 @@
     <t>Материал шелк</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657172/tg-products/wh9xzqswuvwgbmafmluz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657174/tg-products/tze9yngyvqu8mnmasdvh.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657180/tg-products/m7pvci0iacztyp6pr3u7.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657182/tg-products/ommnvpvdo3yckyr5vbst.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657185/tg-products/bfsigfbw8ak8ka48onij.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657188/tg-products/l0gopq2c6musnlcfoz5z.jpg</t>
-  </si>
-  <si>
     <t>Топ Chanel</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657191/tg-products/ppvqbfgli5m1qmlkdpuw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657194/tg-products/a9mwskgzuxgao8coydke.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657197/tg-products/iq1cgfpw5bqfqcwfzyjq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657199/tg-products/oaexxi222us3u7dda6d0.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657202/tg-products/fvclhikjdln1hshxsis1.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657206/tg-products/soyqphkxylqiok1qp2ci.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657208/tg-products/bjdt7gfw682yhvobjcbh.jpg</t>
-  </si>
-  <si>
     <t>Футболка Celine</t>
   </si>
   <si>
     <t>Celine</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657211/tg-products/yfbejf19ousiedoa3ro8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657213/tg-products/gdxmqamyyx5qlu7xkcjk.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657325/tg-products/lxnge5xudt6hxnblg5qt.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657328/tg-products/qs1va9md29sm0hkbimbu.jpg</t>
-  </si>
-  <si>
     <t>Топ Dior</t>
   </si>
   <si>
     <t>20000</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657330/tg-products/a5b9x9ksqrjahiqvzb2d.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657332/tg-products/iqzouoeual1vbxgmuiul.jpg</t>
-  </si>
-  <si>
     <t>Рубашка Prada</t>
   </si>
   <si>
@@ -244,12 +211,6 @@
     <t>Блузка Chloe</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657393/tg-products/jsaz5u3qrqttlngmnfgv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657423/tg-products/godbajmqrjcjbz8prrlc.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657426/tg-products/kpizlbff8kyvcowsrsqj.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657428/tg-products/bouempg5bkozzmhbe2xg.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657430/tg-products/u2nmfiipteo7m94vp7vw.jpg</t>
-  </si>
-  <si>
     <t>Шорты Miumiu</t>
   </si>
   <si>
@@ -262,9 +223,6 @@
     <t>Лонгслив Miumiu</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657434/tg-products/petjj0v2jgsvjhxu2t2y.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657436/tg-products/glwgfyzvoxrivzb8bvrc.jpg</t>
-  </si>
-  <si>
     <t>Cумка Bottega Veneta</t>
   </si>
   <si>
@@ -277,9 +235,6 @@
     <t>bags</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816112/tg-products/pitfg5ru3uln0ddtof3r.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816115/tg-products/lxtt0igpkxfq0wsizh7i.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816337/tg-products/phyafi9uw9fmj6bc1ci7.jpg</t>
-  </si>
-  <si>
     <t>зеленый</t>
   </si>
   <si>
@@ -295,9 +250,6 @@
     <t>Материал нейлон</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816339/tg-products/fsfrtxbtdfo0s02zgsmd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816341/tg-products/jn9iloy9lyux1gyegmxx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816513/tg-products/pakoq54nopsn1hndpde9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816516/tg-products/ayxvxbmsubumkq11iab2.jpg</t>
-  </si>
-  <si>
     <t>Поло Miumiu</t>
   </si>
   <si>
@@ -307,18 +259,9 @@
     <t>Лонгслив Celine</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816630/tg-products/rzhuphpv934hsspwjcac.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816632/tg-products/wcczjq0eafp70qnq7yxb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816635/tg-products/y8abqxdgeqradf9v8kn3.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816898/tg-products/wc9dbqqabjssntstope5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816901/tg-products/nqgnpv4nhjbwiu7hjvtq.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816903/tg-products/di8f3jkcpgga3r9qmcyb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817251/tg-products/i734pcf89hwihtvndvkd.jpg</t>
-  </si>
-  <si>
     <t>Юбка Prada</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817254/tg-products/rizqedb0kzzpw8mad3b6.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817256/tg-products/d1fiiqkepfx7wueogmvt.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817313/tg-products/b7eg1yovz5ynm5blftej.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817315/tg-products/vcl3bibo013ehsgxzfpm.jpg</t>
-  </si>
-  <si>
     <t>Джинсы Brunello Cucinelli</t>
   </si>
   <si>
@@ -328,36 +271,21 @@
     <t>Материал Хлопок</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817318/tg-products/ylgzcd8hw89ryxuy9wgb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817502/tg-products/yxbdwftwbt2nwhpdltis.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817505/tg-products/dbfkikayeksfittpg3c3.jpg</t>
-  </si>
-  <si>
     <t>Рубашка Valentino</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817508/tg-products/w1svjywfln1pih49hg8t.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817642/tg-products/lmdkaqnxyh5f14hohww3.jpg</t>
-  </si>
-  <si>
     <t>Майка Prada</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817645/tg-products/jnynyokfyhj3qsyx9xnj.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817647/tg-products/bfrmyir175yqnr9ob40p.jpg</t>
-  </si>
-  <si>
     <t>черный</t>
   </si>
   <si>
     <t>Рубашка Brunello Cucinelli</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817754/tg-products/cpfreiffmhgyzd93datj.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817756/tg-products/sf2k3vztxn4ic512gzsx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817758/tg-products/jh8oydbviq4dukpfcnu8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817777/tg-products/db51stpkjb9qyt1xf4oa.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817780/tg-products/riy5n5zhqnbwt4pmjth6.jpg</t>
-  </si>
-  <si>
     <t>коричневый</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817782/tg-products/ufiiywegloio1x0gqdup.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830691/tg-products/dhjldil5xwzxwdvvsy4d.jpg</t>
-  </si>
-  <si>
     <t>Кроссовки Hermes</t>
   </si>
   <si>
@@ -367,9 +295,6 @@
     <t>shoes</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830697/tg-products/t58uzuebmuahcobfnwve.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830700/tg-products/rodsy5dk3l0a8xiqcril.jpg</t>
-  </si>
-  <si>
     <t>35 36 37 38 39 40</t>
   </si>
   <si>
@@ -481,60 +406,27 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833016/tg-products/jeoxdlgvx885ilu5ppjy.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833036/tg-products/fwfq56v1fhvye5vn7tca.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833663/tg-products/dqdejnonpwlysoyuulm5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833667/tg-products/ajna4isso0n29hf2pece.jpg</t>
-  </si>
-  <si>
     <t>Сумка Bottega Veneta</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833670/tg-products/hwxadkpms9jh21fxw3jy.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833745/tg-products/p55aadptaigq65lca5gw.jpg</t>
-  </si>
-  <si>
     <t>39x25x18.5 см</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833753/tg-products/n1h2jljzzvnvbb5vuqm9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833757/tg-products/hlit3tg9hcvolmikvqj8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833786/tg-products/itgmxlmrxnmqpluutqyg.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833789/tg-products/hjhf0t97cpv5ikiaachr.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833792/tg-products/i43cheic3jgchzlrutej.jpg</t>
-  </si>
-  <si>
     <t>бордовый</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833835/tg-products/ybmj3n0lwzafivnpl1uw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833838/tg-products/js8z3k0d0dfxtckeecxz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833841/tg-products/ie7ieg44kpg7mqziwb5l.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833909/tg-products/k4pbk87mhwndsrpoz0js.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833913/tg-products/to7x83ks9mydmb4zwzfs.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833917/tg-products/a0zubiodyon2xd1rfik2.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833932/tg-products/fy8m8n6xt24oowu69bdl.jpg</t>
-  </si>
-  <si>
     <t>красный</t>
   </si>
   <si>
     <t>21x11x9 см</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833936/tg-products/kf5evug3y3afwlfsxe7k.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833938/tg-products/uqpacz5ywnypbmulzpad.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833962/tg-products/vxgzb3plkv0lljydi0ql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833965/tg-products/wsn7tqksvlrvoj5odctx.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833969/tg-products/pboh9oo8jcgcnpj5bytv.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834028/tg-products/dll5ilxr2cvrfrmb5zr6.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834031/tg-products/tjayysex8bzeuofpthiq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834035/tg-products/isuda1chzxqhf49cazlb.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834086/tg-products/q4zbjv25kvxpeiurtwb7.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834089/tg-products/ah9ybpq58ps4c5cw1gsc.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834092/tg-products/uy6cqzf4y0uro9otz8hf.jpg</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834321/tg-products/k4bkfhn2f10ssvrtgm5u.jpg</t>
   </si>
   <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834325/tg-products/z3olimdqvrbbchauxyp8.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835308/tg-products/zyxgjrvtjv4ea5yd2whz.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835311/tg-products/nj42wapveufuq94tux7b.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835315/tg-products/ingo8tua2bmu4cjt7m9b.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835498/tg-products/ixvsxn6ng5h39sv1jhkl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835503/tg-products/uyhrzy2a1xgzdlghyspy.jpg</t>
-  </si>
-  <si>
     <t>17x10x6 см</t>
   </si>
   <si>
@@ -550,12 +442,6 @@
     <t>Куртка Brunello Cucinelli</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835561/tg-products/djmln37ynprbvnw9j3kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835567/tg-products/bcloy4laepu7xjnximux.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835577/tg-products/ms4qzopjvfmnvxe4fyql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835610/tg-products/ry6zindmjsnornscgrre.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835614/tg-products/maa475djsqbflpsu43uq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835617/tg-products/xfa7pbpame6l5jhjcy2r.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835759/tg-products/iwhcisnvkwzcfly0mlih.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835767/tg-products/btetnlvzi7jaytlrij2j.jpg</t>
-  </si>
-  <si>
     <t>Пиджак Loro Piana</t>
   </si>
   <si>
@@ -565,7 +451,130 @@
     <t>Материал шерсть</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835773/tg-products/eokilkgoajhxjgjaknxs.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835778/tg-products/auyz4azjhufbybxeoccy.jpg</t>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835773/tg-products/eokilkgoajhxjgjaknxs.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835778/tg-products/auyz4azjhufbybxeoccy.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835767/tg-products/btetnlvzi7jaytlrij2j.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835759/tg-products/iwhcisnvkwzcfly0mlih.jpg</t>
+  </si>
+  <si>
+    <t>Юбка Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835561/tg-products/djmln37ynprbvnw9j3kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835567/tg-products/bcloy4laepu7xjnximux.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg,  https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835577/tg-products/ms4qzopjvfmnvxe4fyql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835610/tg-products/ry6zindmjsnornscgrre.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835614/tg-products/maa475djsqbflpsu43uq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835617/tg-products/xfa7pbpame6l5jhjcy2r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833036/tg-products/fwfq56v1fhvye5vn7tca.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833670/tg-products/hwxadkpms9jh21fxw3jy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833753/tg-products/n1h2jljzzvnvbb5vuqm9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833789/tg-products/hjhf0t97cpv5ikiaachr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833835/tg-products/ybmj3n0lwzafivnpl1uw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833909/tg-products/k4pbk87mhwndsrpoz0js.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833936/tg-products/kf5evug3y3afwlfsxe7k.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833962/tg-products/vxgzb3plkv0lljydi0ql.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834086/tg-products/q4zbjv25kvxpeiurtwb7.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://res.cloudinary.com/dlexrnrhe/image/upload/v1773834028/tg-products/dll5ilxr2cvrfrmb5zr6.jpg </t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835308/tg-products/zyxgjrvtjv4ea5yd2whz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773830697/tg-products/t58uzuebmuahcobfnwve.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817782/tg-products/ufiiywegloio1x0gqdup.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817754/tg-products/cpfreiffmhgyzd93datj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817645/tg-products/jnynyokfyhj3qsyx9xnj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817508/tg-products/w1svjywfln1pih49hg8t.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817318/tg-products/ylgzcd8hw89ryxuy9wgb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816903/tg-products/di8f3jkcpgga3r9qmcyb.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://res.cloudinary.com/dlexrnrhe/image/upload/v1773817254/tg-products/rizqedb0kzzpw8mad3b6.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816630/tg-products/rzhuphpv934hsspwjcac.jpg </t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816339/tg-products/fsfrtxbtdfo0s02zgsmd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657434/tg-products/petjj0v2jgsvjhxu2t2y.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773816112/tg-products/pitfg5ru3uln0ddtof3r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657428/tg-products/bouempg5bkozzmhbe2xg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657393/tg-products/jsaz5u3qrqttlngmnfgv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657330/tg-products/a5b9x9ksqrjahiqvzb2d.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657325/tg-products/lxnge5xudt6hxnblg5qt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657211/tg-products/yfbejf19ousiedoa3ro8.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657191/tg-products/ppvqbfgli5m1qmlkdpuw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657172/tg-products/wh9xzqswuvwgbmafmluz.jpg,</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657167/tg-products/j01zqhctwihp1juowjcy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657159/tg-products/ucwhnnndkjvjj0rfgch7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657152/tg-products/jdsaqx31zr7cjvimmbxg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657098/tg-products/rsyptz7fwqfelmxy6ydw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657079/tg-products/z6chjwosq1tsmqmouhm6.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657069/tg-products/bhgxysknyx1l2jk9u3rn.jpg</t>
   </si>
 </sst>
 </file>
@@ -676,7 +685,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -689,6 +698,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1101,17 +1111,17 @@
       <c r="G5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>23</v>
@@ -1125,34 +1135,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>23</v>
@@ -1166,10 +1176,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
@@ -1183,8 +1193,8 @@
       <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>39</v>
+      <c r="H7" s="11" t="s">
+        <v>183</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -1193,7 +1203,7 @@
         <v>21</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>23</v>
@@ -1207,25 +1217,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>43</v>
+      <c r="H8" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>20</v>
@@ -1234,7 +1244,7 @@
         <v>21</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>23</v>
@@ -1248,25 +1258,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>47</v>
+      <c r="H9" s="11" t="s">
+        <v>181</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>20</v>
@@ -1289,13 +1299,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
@@ -1306,8 +1316,8 @@
       <c r="G10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>51</v>
+      <c r="H10" s="11" t="s">
+        <v>180</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>20</v>
@@ -1330,25 +1340,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>56</v>
+      <c r="H11" s="11" t="s">
+        <v>179</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>20</v>
@@ -1371,25 +1381,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>60</v>
+      <c r="H12" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>20</v>
@@ -1412,13 +1422,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>16</v>
@@ -1429,8 +1439,8 @@
       <c r="G13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>62</v>
+      <c r="H13" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>20</v>
@@ -1453,10 +1463,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -1470,8 +1480,8 @@
       <c r="G14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>65</v>
+      <c r="H14" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>20</v>
@@ -1494,25 +1504,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>66</v>
+      <c r="H15" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>20</v>
@@ -1535,25 +1545,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>69</v>
+      <c r="H16" s="11" t="s">
+        <v>174</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>20</v>
@@ -1576,13 +1586,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>16</v>
@@ -1594,7 +1604,7 @@
         <v>18</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>20</v>
@@ -1603,7 +1613,7 @@
         <v>21</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>23</v>
@@ -1617,25 +1627,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>74</v>
+      <c r="H18" s="11" t="s">
+        <v>173</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>20</v>
@@ -1658,25 +1668,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>75</v>
+      <c r="H19" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>20</v>
@@ -1699,13 +1709,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -1717,7 +1727,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>20</v>
@@ -1726,7 +1736,7 @@
         <v>21</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>23</v>
@@ -1740,10 +1750,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>15</v>
@@ -1757,8 +1767,8 @@
       <c r="G21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>80</v>
+      <c r="H21" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>20</v>
@@ -1767,7 +1777,7 @@
         <v>21</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>23</v>
@@ -1781,25 +1791,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="8">
-        <v>52000</v>
+        <v>68</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>85</v>
+        <v>70</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>20</v>
@@ -1808,10 +1818,10 @@
         <v>21</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="M22" s="10">
         <v>46099</v>
@@ -1822,25 +1832,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="8">
-        <v>39000</v>
+        <v>74</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>91</v>
+      <c r="H23" s="11" t="s">
+        <v>169</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>20</v>
@@ -1863,13 +1873,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="8">
-        <v>13000</v>
+        <v>64</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>16</v>
@@ -1881,7 +1891,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>20</v>
@@ -1890,7 +1900,7 @@
         <v>21</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>23</v>
@@ -1904,10 +1914,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D25" s="8">
         <v>13000</v>
@@ -1921,8 +1931,8 @@
       <c r="G25" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>95</v>
+      <c r="H25" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>20</v>
@@ -1945,10 +1955,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D26" s="8">
         <v>13000</v>
@@ -1962,8 +1972,8 @@
       <c r="G26" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>96</v>
+      <c r="H26" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>20</v>
@@ -1972,7 +1982,7 @@
         <v>21</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>23</v>
@@ -1986,10 +1996,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D27" s="8">
         <v>19000</v>
@@ -2003,8 +2013,8 @@
       <c r="G27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>98</v>
+      <c r="H27" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>20</v>
@@ -2013,7 +2023,7 @@
         <v>21</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>23</v>
@@ -2027,10 +2037,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D28" s="8">
         <v>18000</v>
@@ -2039,13 +2049,13 @@
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>102</v>
+      <c r="H28" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>20</v>
@@ -2054,7 +2064,7 @@
         <v>21</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>23</v>
@@ -2068,10 +2078,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="8">
         <v>19000</v>
@@ -2085,8 +2095,8 @@
       <c r="G29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>104</v>
+      <c r="H29" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>20</v>
@@ -2109,10 +2119,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D30" s="8">
         <v>19000</v>
@@ -2126,8 +2136,8 @@
       <c r="G30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>106</v>
+      <c r="H30" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>20</v>
@@ -2136,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>23</v>
@@ -2150,10 +2160,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D31" s="8">
         <v>32000</v>
@@ -2162,13 +2172,13 @@
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>109</v>
+      <c r="H31" s="11" t="s">
+        <v>162</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>20</v>
@@ -2191,10 +2201,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D32" s="8">
         <v>28000</v>
@@ -2203,13 +2213,13 @@
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>111</v>
+      <c r="H32" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>20</v>
@@ -2218,7 +2228,7 @@
         <v>21</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>23</v>
@@ -2232,10 +2242,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D33" s="8">
         <v>21000</v>
@@ -2244,13 +2254,13 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>115</v>
+        <v>90</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>160</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>20</v>
@@ -2259,10 +2269,10 @@
         <v>21</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="M33" s="10">
         <v>46099</v>
@@ -2273,10 +2283,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D34" s="8">
         <v>24000</v>
@@ -2285,13 +2295,13 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>20</v>
@@ -2300,10 +2310,10 @@
         <v>21</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M34" s="10">
         <v>46099</v>
@@ -2314,10 +2324,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D35" s="8">
         <v>24000</v>
@@ -2326,13 +2336,13 @@
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>20</v>
@@ -2344,7 +2354,7 @@
         <v>22</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M35" s="10">
         <v>46099</v>
@@ -2355,10 +2365,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D36" s="8">
         <v>24000</v>
@@ -2367,13 +2377,13 @@
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>20</v>
@@ -2382,10 +2392,10 @@
         <v>21</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M36" s="10">
         <v>46099</v>
@@ -2396,10 +2406,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D37" s="8">
         <v>24000</v>
@@ -2408,13 +2418,13 @@
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>20</v>
@@ -2423,10 +2433,10 @@
         <v>21</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M37" s="10">
         <v>46099</v>
@@ -2437,10 +2447,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D38" s="8">
         <v>24000</v>
@@ -2449,13 +2459,13 @@
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>20</v>
@@ -2464,10 +2474,10 @@
         <v>21</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M38" s="10">
         <v>46099</v>
@@ -2478,10 +2488,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D39" s="8">
         <v>24000</v>
@@ -2490,13 +2500,13 @@
         <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>20</v>
@@ -2505,10 +2515,10 @@
         <v>21</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M39" s="10">
         <v>46099</v>
@@ -2519,10 +2529,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D40" s="8">
         <v>24000</v>
@@ -2531,13 +2541,13 @@
         <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>20</v>
@@ -2546,10 +2556,10 @@
         <v>21</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M40" s="10">
         <v>46099</v>
@@ -2560,10 +2570,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D41" s="8">
         <v>24000</v>
@@ -2572,13 +2582,13 @@
         <v>16</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>20</v>
@@ -2590,7 +2600,7 @@
         <v>26</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M41" s="10">
         <v>46099</v>
@@ -2601,10 +2611,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D42" s="8">
         <v>24000</v>
@@ -2613,13 +2623,13 @@
         <v>16</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>20</v>
@@ -2628,10 +2638,10 @@
         <v>21</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M42" s="10">
         <v>46099</v>
@@ -2642,10 +2652,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D43" s="8">
         <v>24000</v>
@@ -2654,13 +2664,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>20</v>
@@ -2669,10 +2679,10 @@
         <v>21</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M43" s="10">
         <v>46099</v>
@@ -2683,10 +2693,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D44" s="8">
         <v>24000</v>
@@ -2695,13 +2705,13 @@
         <v>16</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>20</v>
@@ -2710,10 +2720,10 @@
         <v>21</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M44" s="10">
         <v>46099</v>
@@ -2724,10 +2734,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D45" s="8">
         <v>27000</v>
@@ -2736,13 +2746,13 @@
         <v>16</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>20</v>
@@ -2754,7 +2764,7 @@
         <v>22</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M45" s="10">
         <v>46099</v>
@@ -2765,10 +2775,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D46" s="8">
         <v>27000</v>
@@ -2777,13 +2787,13 @@
         <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>20</v>
@@ -2792,10 +2802,10 @@
         <v>21</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M46" s="10">
         <v>46099</v>
@@ -2806,10 +2816,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D47" s="8">
         <v>20000</v>
@@ -2818,13 +2828,13 @@
         <v>16</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>20</v>
@@ -2836,7 +2846,7 @@
         <v>26</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M47" s="10">
         <v>46099</v>
@@ -2847,10 +2857,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D48" s="8">
         <v>20000</v>
@@ -2859,13 +2869,13 @@
         <v>16</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>20</v>
@@ -2874,10 +2884,10 @@
         <v>21</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M48" s="10">
         <v>46099</v>
@@ -2888,10 +2898,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D49" s="8">
         <v>20000</v>
@@ -2900,13 +2910,13 @@
         <v>16</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>20</v>
@@ -2915,10 +2925,10 @@
         <v>21</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="M49" s="10">
         <v>46099</v>
@@ -2929,10 +2939,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D50" s="8">
         <v>55000</v>
@@ -2941,13 +2951,13 @@
         <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>20</v>
@@ -2956,10 +2966,10 @@
         <v>21</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M50" s="10">
         <v>46099</v>
@@ -2970,10 +2980,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D51" s="8">
         <v>55000</v>
@@ -2982,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>20</v>
@@ -2997,10 +3007,10 @@
         <v>21</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M51" s="10">
         <v>46099</v>
@@ -3011,10 +3021,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D52" s="8">
         <v>55000</v>
@@ -3023,13 +3033,13 @@
         <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>20</v>
@@ -3038,10 +3048,10 @@
         <v>21</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M52" s="10">
         <v>46099</v>
@@ -3052,10 +3062,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D53" s="8">
         <v>65000</v>
@@ -3064,13 +3074,13 @@
         <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>20</v>
@@ -3082,7 +3092,7 @@
         <v>22</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M53" s="10">
         <v>46099</v>
@@ -3093,10 +3103,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D54" s="8">
         <v>60000</v>
@@ -3105,13 +3115,13 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>20</v>
@@ -3120,10 +3130,10 @@
         <v>21</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M54" s="10">
         <v>46099</v>
@@ -3134,10 +3144,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D55" s="8">
         <v>60000</v>
@@ -3146,13 +3156,13 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>20</v>
@@ -3161,10 +3171,10 @@
         <v>21</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M55" s="10">
         <v>46099</v>
@@ -3175,10 +3185,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="D56" s="8">
         <v>60000</v>
@@ -3187,13 +3197,13 @@
         <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>20</v>
@@ -3202,10 +3212,10 @@
         <v>21</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M56" s="10">
         <v>46099</v>
@@ -3216,10 +3226,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D57" s="8">
         <v>55000</v>
@@ -3228,13 +3238,13 @@
         <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H57" s="8" t="s">
-        <v>153</v>
+      <c r="H57" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>20</v>
@@ -3243,10 +3253,10 @@
         <v>21</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M57" s="10">
         <v>46099</v>
@@ -3257,10 +3267,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D58" s="8">
         <v>64000</v>
@@ -3269,13 +3279,13 @@
         <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>155</v>
+        <v>70</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="I58" s="8" t="s">
         <v>20</v>
@@ -3287,7 +3297,7 @@
         <v>22</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M58" s="10">
         <v>46099</v>
@@ -3298,10 +3308,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D59" s="8">
         <v>64000</v>
@@ -3310,13 +3320,13 @@
         <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>157</v>
+        <v>70</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>20</v>
@@ -3325,10 +3335,10 @@
         <v>21</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M59" s="10">
         <v>46099</v>
@@ -3339,10 +3349,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D60" s="8">
         <v>64000</v>
@@ -3351,13 +3361,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>158</v>
+        <v>70</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>20</v>
@@ -3366,10 +3376,10 @@
         <v>21</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M60" s="10">
         <v>46099</v>
@@ -3380,10 +3390,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D61" s="8">
         <v>64000</v>
@@ -3392,13 +3402,13 @@
         <v>16</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>160</v>
+        <v>70</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>20</v>
@@ -3407,10 +3417,10 @@
         <v>21</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M61" s="10">
         <v>46099</v>
@@ -3421,10 +3431,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D62" s="8">
         <v>36000</v>
@@ -3433,13 +3443,13 @@
         <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>161</v>
+        <v>70</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>154</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>20</v>
@@ -3448,10 +3458,10 @@
         <v>21</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M62" s="10">
         <v>46099</v>
@@ -3462,10 +3472,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D63" s="8">
         <v>36000</v>
@@ -3474,13 +3484,13 @@
         <v>16</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>164</v>
+        <v>70</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>20</v>
@@ -3489,10 +3499,10 @@
         <v>21</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M63" s="10">
         <v>46099</v>
@@ -3503,10 +3513,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D64" s="8">
         <v>36000</v>
@@ -3515,13 +3525,13 @@
         <v>16</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>165</v>
+        <v>70</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>20</v>
@@ -3530,10 +3540,10 @@
         <v>21</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M64" s="10">
         <v>46099</v>
@@ -3544,10 +3554,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D65" s="8">
         <v>36000</v>
@@ -3556,13 +3566,13 @@
         <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>166</v>
+        <v>70</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>20</v>
@@ -3571,10 +3581,10 @@
         <v>21</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M65" s="10">
         <v>46099</v>
@@ -3585,10 +3595,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D66" s="8">
         <v>36000</v>
@@ -3597,13 +3607,13 @@
         <v>16</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>167</v>
+        <v>70</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>20</v>
@@ -3612,10 +3622,10 @@
         <v>21</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M66" s="10">
         <v>46099</v>
@@ -3626,10 +3636,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D67" s="8">
         <v>21000</v>
@@ -3638,13 +3648,13 @@
         <v>16</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>20</v>
@@ -3656,7 +3666,7 @@
         <v>26</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="M67" s="10">
         <v>46099</v>
@@ -3667,10 +3677,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D68" s="8">
         <v>21000</v>
@@ -3679,13 +3689,13 @@
         <v>16</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>20</v>
@@ -3697,7 +3707,7 @@
         <v>26</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="M68" s="10">
         <v>46099</v>
@@ -3708,10 +3718,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D69" s="8">
         <v>32000</v>
@@ -3720,13 +3730,13 @@
         <v>16</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>170</v>
+        <v>70</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>20</v>
@@ -3735,10 +3745,10 @@
         <v>21</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="M69" s="10">
         <v>46099</v>
@@ -3749,10 +3759,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D70" s="8">
         <v>63000</v>
@@ -3761,13 +3771,13 @@
         <v>16</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="G70" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="I70" s="8" t="s">
         <v>20</v>
@@ -3776,10 +3786,10 @@
         <v>21</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M70" s="10">
         <v>46099</v>
@@ -3790,10 +3800,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D71" s="8">
         <v>36000</v>
@@ -3802,13 +3812,13 @@
         <v>16</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>20</v>
@@ -3820,7 +3830,7 @@
         <v>22</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M71" s="10">
         <v>46099</v>
@@ -3831,10 +3841,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D72" s="8">
         <v>36000</v>
@@ -3843,13 +3853,13 @@
         <v>16</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H72" s="8" t="s">
-        <v>177</v>
+      <c r="H72" s="11" t="s">
+        <v>148</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>20</v>
@@ -3861,7 +3871,7 @@
         <v>22</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M72" s="10">
         <v>46099</v>
@@ -3872,10 +3882,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="D73" s="8">
         <v>25000</v>
@@ -3884,13 +3894,13 @@
         <v>16</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>20</v>
@@ -3902,7 +3912,7 @@
         <v>22</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M73" s="10">
         <v>46099</v>
@@ -4950,6 +4960,43 @@
     <hyperlink ref="H56" r:id="rId30" xr:uid="{1D3BB45C-C7E9-174F-8F72-A00DC3563F84}"/>
     <hyperlink ref="H67" r:id="rId31" xr:uid="{BCA705D2-FDC0-1C4D-8B19-E359DFC50FFF}"/>
     <hyperlink ref="H68" r:id="rId32" xr:uid="{8E93EE4F-9052-A844-916D-D6F1C62AAF47}"/>
+    <hyperlink ref="H72" r:id="rId33" display="https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg" xr:uid="{475D28CB-5EA7-E445-8A81-29A0842BBCF9}"/>
+    <hyperlink ref="H57" r:id="rId34" xr:uid="{11BE95AC-3563-5443-95E9-B98D2CA4FBE3}"/>
+    <hyperlink ref="H58" r:id="rId35" xr:uid="{A8489FD4-C980-F74A-8425-1EE6A56010C1}"/>
+    <hyperlink ref="H59" r:id="rId36" xr:uid="{FE9A185F-5B84-CE46-8AE1-69C1CDF24D3D}"/>
+    <hyperlink ref="H60" r:id="rId37" xr:uid="{E91E591B-05DD-FF42-8BDC-97E775FD0049}"/>
+    <hyperlink ref="H61" r:id="rId38" xr:uid="{C4B3F011-F0E2-6948-986C-9E061116FB9E}"/>
+    <hyperlink ref="H62" r:id="rId39" xr:uid="{AE825DE9-98AE-C643-9AC2-973B335AA197}"/>
+    <hyperlink ref="H63" r:id="rId40" xr:uid="{FB2EDF1A-C2DB-1A42-9895-A5C7022D920F}"/>
+    <hyperlink ref="H64" r:id="rId41" xr:uid="{35B5D7D5-DEF9-C448-9C05-4B69FA7BCE70}"/>
+    <hyperlink ref="H66" r:id="rId42" xr:uid="{D46A5009-693F-2D41-848D-3F9BC95858DD}"/>
+    <hyperlink ref="H65" r:id="rId43" xr:uid="{FD4AF6E4-DC4F-364C-9F4B-7A9B4F54ECA9}"/>
+    <hyperlink ref="H69" r:id="rId44" xr:uid="{AE457894-C6E1-5243-A590-74C71268C011}"/>
+    <hyperlink ref="H33" r:id="rId45" xr:uid="{594321F7-9F4D-1047-B12A-2CB991EA0316}"/>
+    <hyperlink ref="H32" r:id="rId46" xr:uid="{0E5E614B-ADFA-9248-AD14-BF44811E2B60}"/>
+    <hyperlink ref="H31" r:id="rId47" xr:uid="{E4F06C48-6C84-9A47-AD46-0A10654BEB25}"/>
+    <hyperlink ref="H30" r:id="rId48" xr:uid="{7BF14278-EE98-E945-B1BB-B07165BCBF97}"/>
+    <hyperlink ref="H29" r:id="rId49" xr:uid="{83F817CC-B7C6-F245-B4F8-C8CEAB7084E2}"/>
+    <hyperlink ref="H28" r:id="rId50" xr:uid="{502C56AC-B5B1-144D-AB5C-E2528F8C8A5C}"/>
+    <hyperlink ref="H26" r:id="rId51" xr:uid="{448202B5-2D9F-214E-B534-6C652898B069}"/>
+    <hyperlink ref="H27" r:id="rId52" xr:uid="{BACD3E75-FC57-8D4C-AE21-7CCBE55393F5}"/>
+    <hyperlink ref="H25" r:id="rId53" xr:uid="{41CAA107-54AE-7245-9C76-7AFD8B093580}"/>
+    <hyperlink ref="H23" r:id="rId54" xr:uid="{F83164A8-CB7B-714C-9673-C5DB38B8726A}"/>
+    <hyperlink ref="H21" r:id="rId55" xr:uid="{3720409C-694C-F24F-BC82-3BF533187DB5}"/>
+    <hyperlink ref="H22" r:id="rId56" xr:uid="{3BBA25AD-84A8-F545-B7C6-A8BCD20C0193}"/>
+    <hyperlink ref="H19" r:id="rId57" xr:uid="{1C22F573-F7B1-984F-9769-5F0002B9CE9B}"/>
+    <hyperlink ref="H18" r:id="rId58" xr:uid="{BCBFE71D-030F-AE4E-9178-AEED804BA399}"/>
+    <hyperlink ref="H16" r:id="rId59" xr:uid="{C7540697-781F-AA46-AB0D-81D2BEE98CD5}"/>
+    <hyperlink ref="H15" r:id="rId60" xr:uid="{5208BA8B-3351-F340-9C08-AE2F16F7BF62}"/>
+    <hyperlink ref="H14" r:id="rId61" xr:uid="{54921A81-B696-EC40-B773-DA445DA1556F}"/>
+    <hyperlink ref="H13" r:id="rId62" xr:uid="{1F04152C-9072-B242-A5CF-D6AFA14CABA5}"/>
+    <hyperlink ref="H12" r:id="rId63" xr:uid="{8B155CE8-066E-3241-82E3-B6202D63041B}"/>
+    <hyperlink ref="H11" r:id="rId64" xr:uid="{5E8AC82B-CABC-A444-BE5F-1AD24F1D1839}"/>
+    <hyperlink ref="H10" r:id="rId65" xr:uid="{4C0B6705-6286-A741-BB53-1B9062FF53C0}"/>
+    <hyperlink ref="H9" r:id="rId66" xr:uid="{C1C9F9B3-829D-E545-AF66-013A250A217E}"/>
+    <hyperlink ref="H8" r:id="rId67" xr:uid="{BC392C16-44E5-0247-9603-E28D1664E0BC}"/>
+    <hyperlink ref="H7" r:id="rId68" xr:uid="{BEC9B471-A176-CF47-9FCA-E2FA242AA85A}"/>
+    <hyperlink ref="H5" r:id="rId69" xr:uid="{97C5CAB9-0FD9-2E44-87D6-AEDA82ABBA70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2D99DD-513E-7C48-BBEA-C430C895E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0D2ACE-2770-6F43-9720-9CD3B078663E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="255">
   <si>
     <t>id</t>
   </si>
@@ -466,9 +466,6 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835561/tg-products/djmln37ynprbvnw9j3kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835567/tg-products/bcloy4laepu7xjnximux.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg,  https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835577/tg-products/ms4qzopjvfmnvxe4fyql.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835610/tg-products/ry6zindmjsnornscgrre.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835614/tg-products/maa475djsqbflpsu43uq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835617/tg-products/xfa7pbpame6l5jhjcy2r.jpg</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773833036/tg-products/fwfq56v1fhvye5vn7tca.jpg</t>
   </si>
   <si>
@@ -575,6 +572,219 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773657069/tg-products/bhgxysknyx1l2jk9u3rn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835622/tg-products/xpswgt46xryxgyiizb5q.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835610/tg-products/ry6zindmjsnornscgrre.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835614/tg-products/maa475djsqbflpsu43uq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773835617/tg-products/xfa7pbpame6l5jhjcy2r.jpg</t>
+  </si>
+  <si>
+    <t>Футболка Loewe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773914971/tg-products/d1salpeehkzhhihxoanc.jpg</t>
+  </si>
+  <si>
+    <t>Рубашка Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773914978/tg-products/vb1w8lhiclcmlq3sdyr1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773914986/tg-products/z4wejuwnxlxhnczb0o21.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773914995/tg-products/plvk8isxl2lp6o6uquml.jpg</t>
+  </si>
+  <si>
+    <t>Футболка Hermes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915004/tg-products/bjyujibnpchdpqt3l4bg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915010/tg-products/akcys7bv9vxcmdeppsuk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915133/tg-products/qq6oo9af9mwumggnc1qz.jpg</t>
+  </si>
+  <si>
+    <t>Сумка Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915641/tg-products/stkyhzzdkuh1cgimaizl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915643/tg-products/tzko9pcwffbbwbbufkfv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915648/tg-products/uf0pp82dkddefxuqld1s.jpg</t>
+  </si>
+  <si>
+    <t>23х14х6 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915701/tg-products/bvup6c9kmi4zlzidrgyq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915713/tg-products/qmmjhrb4i7hnshqgbiyb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915721/tg-products/rqlei70guawavf6fhzjo.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915768/tg-products/xalpgyleamdxmb1oyzq9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915771/tg-products/fumo4n1kyawnlcva1nif.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915786/tg-products/c53oo1tsfepwatxfoqdc.jpg</t>
+  </si>
+  <si>
+    <t>17х14х8 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915974/tg-products/okpiwinqf4jcsf7nr3hf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915983/tg-products/hqs27dixwbs9zfsletjk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915992/tg-products/klvb2yk28squrw4eqcoe.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916026/tg-products/v3bzscftxxtfkok5cdaf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916040/tg-products/cul4h6zea2sonxd1lgxf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916055/tg-products/mffin77lcud3f2op2cyd.jpg</t>
+  </si>
+  <si>
+    <t>22х20х13 см</t>
+  </si>
+  <si>
+    <t>Материал ткань</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916102/tg-products/fnje0ov6zeyrfokmxdks.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916113/tg-products/cgpw0axs1slqut7jrnrk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916132/tg-products/tbbqejtlrdnzpynr0nws.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916086/tg-products/sddmxitn3mxmgthy2cp1.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916093/tg-products/wxfglpoym9jkav8kz9kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916138/tg-products/qlzplygyrsjonuc6kiqk.jpg</t>
+  </si>
+  <si>
+    <t>Рюкзак Miumiu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916432/tg-products/l1wohpgzi9o8rnu80flv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916436/tg-products/mrmuffh9c6uvbhg9s7rk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916445/tg-products/ilk8cs62va6xydzdmstw.jpg</t>
+  </si>
+  <si>
+    <t>30х25х13 см</t>
+  </si>
+  <si>
+    <t>Материал черный</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916474/tg-products/afceszq8os8lberkmalm.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916485/tg-products/p9uxynpkqbn2efirha2t.jpg</t>
+  </si>
+  <si>
+    <t>Сумка Miumiu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916495/tg-products/rdgkfra33efqfoebrgka.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916513/tg-products/e0ebomobixo7w1mjg5jk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916521/tg-products/l9jpafud4kicigrgexwc.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916526/tg-products/lfhgnrx8fx2bayw4d0ve.jpg</t>
+  </si>
+  <si>
+    <t>44х23х14 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916555/tg-products/pwqnaichbddjbn9oapdd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916564/tg-products/znxg24dqz9iogwltnsg8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916590/tg-products/ot81lsalffufeiq8rks1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916922/tg-products/eootmyjtcnsi4yr4m62z.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916929/tg-products/fotezp5mzile8hxif7dl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916940/tg-products/ghkrsbfqxkpdjudellin.jpg</t>
+  </si>
+  <si>
+    <t>33х19х5 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916978/tg-products/l1haqfjdigfv4gznyeea.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg</t>
+  </si>
+  <si>
+    <t>серый</t>
+  </si>
+  <si>
+    <t>Топ Fendi</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933748/tg-products/xdb2jkfqk6wesecqdolt.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933749/tg-products/mgcrk3utqbezfs4ixztw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933756/tg-products/yiu9q66cs6mwcfahauri.jpg</t>
+  </si>
+  <si>
+    <t>Рубашка Fendi</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933794/tg-products/bdl0j9ioh5mayldrjmfw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933795/tg-products/enspkgek73kduyxzd0e9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933796/tg-products/hvt9ykb7wv9vwn2fegto.jpg</t>
+  </si>
+  <si>
+    <t>Свитер Hermes</t>
+  </si>
+  <si>
+    <t>Материал хлопок и шелк</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933843/tg-products/tqqmzddc6gtpkhmpksex.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933844/tg-products/zezm4sstdkbsfkloqbx4.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933846/tg-products/oc7cxfwca0ogmwaem0wp.jpg</t>
+  </si>
+  <si>
+    <t>Поло Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933876/tg-products/fuldr5oxwjl4ofjtyvb5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933881/tg-products/zxsbuqp1zi6fmudrcrge.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933882/tg-products/ibvz2vhk5zjttfjncoju.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933931/tg-products/y3preqgf4yrmzvjiabuh.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933932/tg-products/ko7czxgykv0usognjmff.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933933/tg-products/bnlf6iyyg9u6mlqciplj.jpg</t>
+  </si>
+  <si>
+    <t>Платье Louis Vuitton</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773934457/tg-products/ltj8m2vwgmhol94h9ood.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940115/tg-products/zynb4me8jy8291jyhwo9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940116/tg-products/guma9ms2hjqdeypzy08k.jpg</t>
+  </si>
+  <si>
+    <t>Лоферы Loro Piana</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940128/tg-products/rjupb6z4rvxu26o3iptv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940133/tg-products/buiap7kz84pnau6b7d1e.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940139/tg-products/xuxunnpxdjvvdhyyvadl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940149/tg-products/kxqmw1dnvgaygedtqeaw.jpg</t>
+  </si>
+  <si>
+    <t>Лоферы Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940167/tg-products/vfqr3udjudlkjyohduwn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940188/tg-products/epxsyy8fjnuhfzn9rirj.jpg</t>
+  </si>
+  <si>
+    <t>Ботинки Celine</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940219/tg-products/l3e2d1kkyzdxysui3ov2.jpg</t>
+  </si>
+  <si>
+    <t>Ботинки Chanel</t>
+  </si>
+  <si>
+    <t>Материал резина</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940244/tg-products/l8nrk9ffjse9je0bh93x.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940263/tg-products/htcis0dfvogocejsezlt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940338/tg-products/xahkvzjmg8ygpigezbav.jpg</t>
+  </si>
+  <si>
+    <t>22х15х7 см</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940418/tg-products/o9edgik4to8axapcxs0d.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940424/tg-products/pogpzdov1xuj4diavlax.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940439/tg-products/wzb88maxjbg22dqj3q4g.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940473/tg-products/towwzks0ieiqlxisqeue.jpg</t>
+  </si>
+  <si>
+    <t>17х11х5 см</t>
+  </si>
+  <si>
+    <t>Fendi</t>
+  </si>
+  <si>
+    <t>Louis Vuitton</t>
   </si>
 </sst>
 </file>
@@ -715,10 +925,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1112,7 +1318,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -1194,7 +1400,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -1235,7 +1441,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>20</v>
@@ -1276,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>20</v>
@@ -1317,7 +1523,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>20</v>
@@ -1358,7 +1564,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>20</v>
@@ -1399,7 +1605,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>20</v>
@@ -1440,7 +1646,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>20</v>
@@ -1481,7 +1687,7 @@
         <v>18</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>20</v>
@@ -1522,7 +1728,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>20</v>
@@ -1563,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>20</v>
@@ -1645,7 +1851,7 @@
         <v>18</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>20</v>
@@ -1686,7 +1892,7 @@
         <v>18</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>20</v>
@@ -1768,7 +1974,7 @@
         <v>18</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>20</v>
@@ -1809,7 +2015,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>20</v>
@@ -1850,7 +2056,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>20</v>
@@ -1932,7 +2138,7 @@
         <v>18</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>20</v>
@@ -1973,7 +2179,7 @@
         <v>18</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>20</v>
@@ -2014,7 +2220,7 @@
         <v>18</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>20</v>
@@ -2055,7 +2261,7 @@
         <v>18</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>20</v>
@@ -2096,7 +2302,7 @@
         <v>18</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>20</v>
@@ -2137,7 +2343,7 @@
         <v>18</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>20</v>
@@ -2178,7 +2384,7 @@
         <v>18</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>20</v>
@@ -2219,7 +2425,7 @@
         <v>18</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>20</v>
@@ -2260,7 +2466,7 @@
         <v>90</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>20</v>
@@ -3244,7 +3450,7 @@
         <v>18</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>20</v>
@@ -3285,7 +3491,7 @@
         <v>70</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I58" s="8" t="s">
         <v>20</v>
@@ -3326,7 +3532,7 @@
         <v>70</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>20</v>
@@ -3367,7 +3573,7 @@
         <v>70</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>20</v>
@@ -3408,7 +3614,7 @@
         <v>70</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>20</v>
@@ -3449,7 +3655,7 @@
         <v>70</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>20</v>
@@ -3490,7 +3696,7 @@
         <v>70</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>20</v>
@@ -3531,7 +3737,7 @@
         <v>70</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>20</v>
@@ -3572,7 +3778,7 @@
         <v>70</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>20</v>
@@ -3613,7 +3819,7 @@
         <v>70</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>20</v>
@@ -3736,7 +3942,7 @@
         <v>70</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>20</v>
@@ -3859,7 +4065,7 @@
         <v>18</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>20</v>
@@ -3919,566 +4125,1646 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M74" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="8">
+        <v>14000</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M75" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M76" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M77" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="8">
+        <v>13000</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M78" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D79" s="8">
+        <v>11000</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M79" s="10">
+        <v>46100</v>
+      </c>
     </row>
     <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-    </row>
-    <row r="81" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-    </row>
-    <row r="82" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-    </row>
-    <row r="83" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-    </row>
-    <row r="84" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-    </row>
-    <row r="85" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-    </row>
-    <row r="86" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8"/>
-    </row>
-    <row r="87" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-    </row>
-    <row r="88" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-    </row>
-    <row r="89" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
-    </row>
-    <row r="90" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-    </row>
-    <row r="91" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-    </row>
-    <row r="92" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-    </row>
-    <row r="93" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-    </row>
-    <row r="94" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-    </row>
-    <row r="95" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-    </row>
-    <row r="96" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-    </row>
-    <row r="97" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-    </row>
-    <row r="98" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-    </row>
-    <row r="99" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-    </row>
-    <row r="100" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-    </row>
-    <row r="101" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-    </row>
-    <row r="102" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
-    </row>
-    <row r="103" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-    </row>
-    <row r="104" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
-    </row>
-    <row r="105" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-    </row>
-    <row r="106" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-    </row>
-    <row r="107" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="8"/>
-    </row>
-    <row r="108" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
-    </row>
-    <row r="109" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="8"/>
-    </row>
-    <row r="110" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
-    </row>
-    <row r="111" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="8"/>
-    </row>
-    <row r="112" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="8"/>
-    </row>
-    <row r="113" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="8"/>
-    </row>
-    <row r="114" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M80" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="M81" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="M82" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" s="8">
+        <v>68000</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="M83" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="M84" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="M85" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K86" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="M86" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D87" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="M87" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D88" s="8">
+        <v>56000</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L88" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="M88" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D89" s="8">
+        <v>56000</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="M89" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D90" s="8">
+        <v>54000</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="M90" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D91" s="8">
+        <v>54000</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="M91" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D92" s="8">
+        <v>49000</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="M92" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D93" s="8">
+        <v>49000</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="M93" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D94" s="8">
+        <v>17000</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K94" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M94" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D95" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M95" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="8">
+        <v>28000</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M96" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D97" s="8">
+        <v>12500</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M97" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="8">
+        <v>55000</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M98" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D99" s="8">
+        <v>40000</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M99" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H100" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M100" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D101" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H101" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M101" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D102" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H102" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M102" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D103" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M103" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D104" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J104" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K104" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M104" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K105" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M105" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D106" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K106" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M106" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D107" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M107" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K108" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M108" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D109" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M109" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D110" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M110" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D111" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M111" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D112" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M112" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D113" s="8">
+        <v>80000</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="M113" s="10">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
@@ -4492,7 +5778,7 @@
       <c r="L114" s="8"/>
       <c r="M114" s="8"/>
     </row>
-    <row r="115" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
@@ -4506,7 +5792,7 @@
       <c r="L115" s="8"/>
       <c r="M115" s="8"/>
     </row>
-    <row r="116" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
@@ -4520,7 +5806,7 @@
       <c r="L116" s="8"/>
       <c r="M116" s="8"/>
     </row>
-    <row r="117" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
@@ -4534,7 +5820,7 @@
       <c r="L117" s="8"/>
       <c r="M117" s="8"/>
     </row>
-    <row r="118" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -4548,7 +5834,7 @@
       <c r="L118" s="8"/>
       <c r="M118" s="8"/>
     </row>
-    <row r="119" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
@@ -4562,7 +5848,7 @@
       <c r="L119" s="8"/>
       <c r="M119" s="8"/>
     </row>
-    <row r="120" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
@@ -4576,7 +5862,7 @@
       <c r="L120" s="8"/>
       <c r="M120" s="8"/>
     </row>
-    <row r="121" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
@@ -4590,7 +5876,7 @@
       <c r="L121" s="8"/>
       <c r="M121" s="8"/>
     </row>
-    <row r="122" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
@@ -4604,7 +5890,7 @@
       <c r="L122" s="8"/>
       <c r="M122" s="8"/>
     </row>
-    <row r="123" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
@@ -4618,7 +5904,7 @@
       <c r="L123" s="8"/>
       <c r="M123" s="8"/>
     </row>
-    <row r="124" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
@@ -4632,7 +5918,7 @@
       <c r="L124" s="8"/>
       <c r="M124" s="8"/>
     </row>
-    <row r="125" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
@@ -4646,7 +5932,7 @@
       <c r="L125" s="8"/>
       <c r="M125" s="8"/>
     </row>
-    <row r="126" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
@@ -4660,7 +5946,7 @@
       <c r="L126" s="8"/>
       <c r="M126" s="8"/>
     </row>
-    <row r="127" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
@@ -4674,7 +5960,7 @@
       <c r="L127" s="8"/>
       <c r="M127" s="8"/>
     </row>
-    <row r="128" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
@@ -4997,6 +6283,27 @@
     <hyperlink ref="H8" r:id="rId67" xr:uid="{BC392C16-44E5-0247-9603-E28D1664E0BC}"/>
     <hyperlink ref="H7" r:id="rId68" xr:uid="{BEC9B471-A176-CF47-9FCA-E2FA242AA85A}"/>
     <hyperlink ref="H5" r:id="rId69" xr:uid="{97C5CAB9-0FD9-2E44-87D6-AEDA82ABBA70}"/>
+    <hyperlink ref="H74" r:id="rId70" xr:uid="{355C4807-A326-4049-8B18-EC4BCCEA6771}"/>
+    <hyperlink ref="H75" r:id="rId71" xr:uid="{B4C967E2-25EB-224A-9375-D5553A65BDEC}"/>
+    <hyperlink ref="H76" r:id="rId72" xr:uid="{2047E8E9-D291-0147-A1AE-D2247FC8E7B7}"/>
+    <hyperlink ref="H77" r:id="rId73" xr:uid="{57F780E1-013A-B44B-A78A-8E13971240FA}"/>
+    <hyperlink ref="H78" r:id="rId74" xr:uid="{1FD5469F-F1A8-C74A-AF18-780AB15ADA48}"/>
+    <hyperlink ref="H79" r:id="rId75" xr:uid="{FDA055D6-AEAC-A848-86A9-941A9B5E6677}"/>
+    <hyperlink ref="H80" r:id="rId76" xr:uid="{7977804C-3A1F-EB43-AC0B-2A16CC437FED}"/>
+    <hyperlink ref="H100" r:id="rId77" xr:uid="{F6A44307-984E-9E4A-BB29-2096E232D52E}"/>
+    <hyperlink ref="H101" r:id="rId78" xr:uid="{BBB7AEA8-A3E7-2540-9D64-555CF198F0AE}"/>
+    <hyperlink ref="H102" r:id="rId79" xr:uid="{31638D57-F9A1-8440-8AAA-FB7EC3275284}"/>
+    <hyperlink ref="H103" r:id="rId80" xr:uid="{4D67B34A-C716-1048-B21D-FD65FA1FC86A}"/>
+    <hyperlink ref="H104" r:id="rId81" xr:uid="{4F9974E9-281F-324B-B2B6-DB64B7988717}"/>
+    <hyperlink ref="H105" r:id="rId82" xr:uid="{790876C7-43B0-1641-9648-4DA5B66C4E6A}"/>
+    <hyperlink ref="H106" r:id="rId83" xr:uid="{D645509F-DAD4-1B48-AE27-1756FF478CC6}"/>
+    <hyperlink ref="H107" r:id="rId84" xr:uid="{329E350C-1CF8-5C45-95C6-4C3E372F91C2}"/>
+    <hyperlink ref="H108" r:id="rId85" xr:uid="{469EFC21-E4CF-EA44-97D3-E3BC30FBA948}"/>
+    <hyperlink ref="H109" r:id="rId86" xr:uid="{6F4FFC68-88CD-BF45-B17F-2DF461BC021E}"/>
+    <hyperlink ref="H110" r:id="rId87" xr:uid="{234BD536-ADCB-C642-AC40-BC68C8BC75ED}"/>
+    <hyperlink ref="H111" r:id="rId88" xr:uid="{0F913E7E-15FD-6443-9176-9E98916E93F7}"/>
+    <hyperlink ref="H112" r:id="rId89" xr:uid="{7560FF78-E43C-8F41-8F50-98A5F3538B83}"/>
+    <hyperlink ref="H113" r:id="rId90" xr:uid="{97F9E249-BE09-A44A-9460-BA5D56C0AF7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0D2ACE-2770-6F43-9720-9CD3B078663E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349938B9-A317-C343-A87F-1BFEE5D34AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,45 +610,27 @@
     <t>Сумка Chanel</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915641/tg-products/stkyhzzdkuh1cgimaizl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915643/tg-products/tzko9pcwffbbwbbufkfv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915648/tg-products/uf0pp82dkddefxuqld1s.jpg</t>
-  </si>
-  <si>
     <t>23х14х6 см</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915701/tg-products/bvup6c9kmi4zlzidrgyq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915713/tg-products/qmmjhrb4i7hnshqgbiyb.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915721/tg-products/rqlei70guawavf6fhzjo.jpg</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915768/tg-products/xalpgyleamdxmb1oyzq9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915771/tg-products/fumo4n1kyawnlcva1nif.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915786/tg-products/c53oo1tsfepwatxfoqdc.jpg</t>
   </si>
   <si>
     <t>17х14х8 см</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915974/tg-products/okpiwinqf4jcsf7nr3hf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915983/tg-products/hqs27dixwbs9zfsletjk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915992/tg-products/klvb2yk28squrw4eqcoe.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916026/tg-products/v3bzscftxxtfkok5cdaf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916040/tg-products/cul4h6zea2sonxd1lgxf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916055/tg-products/mffin77lcud3f2op2cyd.jpg</t>
-  </si>
-  <si>
     <t>22х20х13 см</t>
   </si>
   <si>
     <t>Материал ткань</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916102/tg-products/fnje0ov6zeyrfokmxdks.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916113/tg-products/cgpw0axs1slqut7jrnrk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916132/tg-products/tbbqejtlrdnzpynr0nws.jpg</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916086/tg-products/sddmxitn3mxmgthy2cp1.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916093/tg-products/wxfglpoym9jkav8kz9kf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916138/tg-products/qlzplygyrsjonuc6kiqk.jpg</t>
   </si>
   <si>
     <t>Рюкзак Miumiu</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916432/tg-products/l1wohpgzi9o8rnu80flv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916436/tg-products/mrmuffh9c6uvbhg9s7rk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916445/tg-products/ilk8cs62va6xydzdmstw.jpg</t>
-  </si>
-  <si>
     <t>30х25х13 см</t>
   </si>
   <si>
@@ -670,15 +652,9 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916555/tg-products/pwqnaichbddjbn9oapdd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916564/tg-products/znxg24dqz9iogwltnsg8.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916590/tg-products/ot81lsalffufeiq8rks1.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916922/tg-products/eootmyjtcnsi4yr4m62z.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916929/tg-products/fotezp5mzile8hxif7dl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916940/tg-products/ghkrsbfqxkpdjudellin.jpg</t>
-  </si>
-  <si>
     <t>33х19х5 см</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916978/tg-products/l1haqfjdigfv4gznyeea.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg</t>
-  </si>
-  <si>
     <t>серый</t>
   </si>
   <si>
@@ -785,6 +761,30 @@
   </si>
   <si>
     <t>Louis Vuitton</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915648/tg-products/uf0pp82dkddefxuqld1s.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915641/tg-products/stkyhzzdkuh1cgimaizl.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915643/tg-products/tzko9pcwffbbwbbufkfv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915721/tg-products/rqlei70guawavf6fhzjo.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915701/tg-products/bvup6c9kmi4zlzidrgyq.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915713/tg-products/qmmjhrb4i7hnshqgbiyb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915983/tg-products/hqs27dixwbs9zfsletjk.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915992/tg-products/klvb2yk28squrw4eqcoe.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915974/tg-products/okpiwinqf4jcsf7nr3hf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916055/tg-products/mffin77lcud3f2op2cyd.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916026/tg-products/v3bzscftxxtfkok5cdaf.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916040/tg-products/cul4h6zea2sonxd1lgxf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916132/tg-products/tbbqejtlrdnzpynr0nws.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916102/tg-products/fnje0ov6zeyrfokmxdks.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916113/tg-products/cgpw0axs1slqut7jrnrk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916445/tg-products/ilk8cs62va6xydzdmstw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916432/tg-products/l1wohpgzi9o8rnu80flv.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916436/tg-products/mrmuffh9c6uvbhg9s7rk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916978/tg-products/l1haqfjdigfv4gznyeea.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916922/tg-products/eootmyjtcnsi4yr4m62z.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916929/tg-products/fotezp5mzile8hxif7dl.jpg</t>
   </si>
 </sst>
 </file>
@@ -4434,7 +4434,7 @@
         <v>70</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>20</v>
@@ -4446,7 +4446,7 @@
         <v>87</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M81" s="10">
         <v>46100</v>
@@ -4475,7 +4475,7 @@
         <v>70</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>20</v>
@@ -4484,10 +4484,10 @@
         <v>21</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M82" s="10">
         <v>46100</v>
@@ -4516,7 +4516,7 @@
         <v>70</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>20</v>
@@ -4528,7 +4528,7 @@
         <v>130</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M83" s="10">
         <v>46100</v>
@@ -4557,7 +4557,7 @@
         <v>70</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>20</v>
@@ -4569,7 +4569,7 @@
         <v>30</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M84" s="10">
         <v>46100</v>
@@ -4598,7 +4598,7 @@
         <v>70</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>20</v>
@@ -4610,7 +4610,7 @@
         <v>85</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M85" s="10">
         <v>46100</v>
@@ -4633,13 +4633,13 @@
         <v>16</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>70</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>20</v>
@@ -4651,7 +4651,7 @@
         <v>41</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M86" s="10">
         <v>46100</v>
@@ -4680,7 +4680,7 @@
         <v>70</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>20</v>
@@ -4692,7 +4692,7 @@
         <v>30</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M87" s="10">
         <v>46100</v>
@@ -4703,7 +4703,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>64</v>
@@ -4721,7 +4721,7 @@
         <v>70</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>20</v>
@@ -4733,7 +4733,7 @@
         <v>87</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M88" s="10">
         <v>46100</v>
@@ -4744,7 +4744,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>64</v>
@@ -4756,13 +4756,13 @@
         <v>16</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>70</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>20</v>
@@ -4774,7 +4774,7 @@
         <v>87</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M89" s="10">
         <v>46100</v>
@@ -4785,7 +4785,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>64</v>
@@ -4803,7 +4803,7 @@
         <v>70</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>20</v>
@@ -4815,7 +4815,7 @@
         <v>85</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M90" s="10">
         <v>46100</v>
@@ -4826,7 +4826,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>64</v>
@@ -4844,7 +4844,7 @@
         <v>70</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>20</v>
@@ -4856,7 +4856,7 @@
         <v>87</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M91" s="10">
         <v>46100</v>
@@ -4867,7 +4867,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>64</v>
@@ -4885,7 +4885,7 @@
         <v>70</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>20</v>
@@ -4897,7 +4897,7 @@
         <v>85</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M92" s="10">
         <v>46100</v>
@@ -4908,7 +4908,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>64</v>
@@ -4926,7 +4926,7 @@
         <v>70</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>20</v>
@@ -4938,7 +4938,7 @@
         <v>87</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="M93" s="10">
         <v>46100</v>
@@ -4949,10 +4949,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D94" s="8">
         <v>17000</v>
@@ -4967,7 +4967,7 @@
         <v>18</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>20</v>
@@ -4990,10 +4990,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D95" s="8">
         <v>25000</v>
@@ -5008,7 +5008,7 @@
         <v>18</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>20</v>
@@ -5031,7 +5031,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>89</v>
@@ -5043,13 +5043,13 @@
         <v>16</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>20</v>
@@ -5072,7 +5072,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>60</v>
@@ -5090,7 +5090,7 @@
         <v>18</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>20</v>
@@ -5131,7 +5131,7 @@
         <v>18</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>20</v>
@@ -5154,10 +5154,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D99" s="8">
         <v>40000</v>
@@ -5172,7 +5172,7 @@
         <v>18</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>20</v>
@@ -5195,7 +5195,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>141</v>
@@ -5213,7 +5213,7 @@
         <v>90</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>20</v>
@@ -5236,7 +5236,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>141</v>
@@ -5254,7 +5254,7 @@
         <v>90</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="I101" s="8" t="s">
         <v>20</v>
@@ -5277,7 +5277,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>141</v>
@@ -5295,7 +5295,7 @@
         <v>90</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I102" s="8" t="s">
         <v>20</v>
@@ -5318,7 +5318,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>141</v>
@@ -5336,7 +5336,7 @@
         <v>90</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I103" s="8" t="s">
         <v>20</v>
@@ -5359,7 +5359,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>48</v>
@@ -5377,7 +5377,7 @@
         <v>90</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>20</v>
@@ -5400,7 +5400,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>48</v>
@@ -5418,7 +5418,7 @@
         <v>90</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>20</v>
@@ -5441,7 +5441,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>48</v>
@@ -5459,7 +5459,7 @@
         <v>90</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I106" s="8" t="s">
         <v>20</v>
@@ -5482,7 +5482,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>48</v>
@@ -5494,13 +5494,13 @@
         <v>16</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>90</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I107" s="8" t="s">
         <v>20</v>
@@ -5523,7 +5523,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>48</v>
@@ -5535,13 +5535,13 @@
         <v>16</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>90</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I108" s="8" t="s">
         <v>20</v>
@@ -5582,7 +5582,7 @@
         <v>70</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I109" s="8" t="s">
         <v>20</v>
@@ -5594,7 +5594,7 @@
         <v>130</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="M109" s="10">
         <v>46100</v>
@@ -5623,7 +5623,7 @@
         <v>70</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I110" s="8" t="s">
         <v>20</v>
@@ -5635,7 +5635,7 @@
         <v>85</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="M110" s="10">
         <v>46100</v>
@@ -5664,7 +5664,7 @@
         <v>70</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I111" s="8" t="s">
         <v>20</v>
@@ -5676,7 +5676,7 @@
         <v>96</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="M111" s="10">
         <v>46100</v>
@@ -5705,7 +5705,7 @@
         <v>70</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I112" s="8" t="s">
         <v>20</v>
@@ -5717,7 +5717,7 @@
         <v>30</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="M112" s="10">
         <v>46100</v>
@@ -5746,7 +5746,7 @@
         <v>70</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I113" s="8" t="s">
         <v>20</v>
@@ -5758,7 +5758,7 @@
         <v>26</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="M113" s="10">
         <v>46100</v>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349938B9-A317-C343-A87F-1BFEE5D34AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCBA49C-6C8A-2249-AAC7-D26080679A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="254">
   <si>
     <t>id</t>
   </si>
@@ -604,9 +604,6 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915010/tg-products/akcys7bv9vxcmdeppsuk.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773915133/tg-products/qq6oo9af9mwumggnc1qz.jpg</t>
-  </si>
-  <si>
     <t>Сумка Chanel</t>
   </si>
   <si>
@@ -661,15 +658,9 @@
     <t>Топ Fendi</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933748/tg-products/xdb2jkfqk6wesecqdolt.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933749/tg-products/mgcrk3utqbezfs4ixztw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933756/tg-products/yiu9q66cs6mwcfahauri.jpg</t>
-  </si>
-  <si>
     <t>Рубашка Fendi</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933794/tg-products/bdl0j9ioh5mayldrjmfw.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933795/tg-products/enspkgek73kduyxzd0e9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933796/tg-products/hvt9ykb7wv9vwn2fegto.jpg</t>
-  </si>
-  <si>
     <t>Свитер Hermes</t>
   </si>
   <si>
@@ -685,15 +676,9 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933876/tg-products/fuldr5oxwjl4ofjtyvb5.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933881/tg-products/zxsbuqp1zi6fmudrcrge.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933882/tg-products/ibvz2vhk5zjttfjncoju.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933931/tg-products/y3preqgf4yrmzvjiabuh.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933932/tg-products/ko7czxgykv0usognjmff.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933933/tg-products/bnlf6iyyg9u6mlqciplj.jpg</t>
-  </si>
-  <si>
     <t>Платье Louis Vuitton</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773934457/tg-products/ltj8m2vwgmhol94h9ood.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940115/tg-products/zynb4me8jy8291jyhwo9.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773940116/tg-products/guma9ms2hjqdeypzy08k.jpg</t>
-  </si>
-  <si>
     <t>Лоферы Loro Piana</t>
   </si>
   <si>
@@ -784,7 +769,19 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916978/tg-products/l1haqfjdigfv4gznyeea.jpg</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773917006/tg-products/dtnurtt0jdklt6jjovtn.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916922/tg-products/eootmyjtcnsi4yr4m62z.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773916929/tg-products/fotezp5mzile8hxif7dl.jpg</t>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933749/tg-products/mgcrk3utqbezfs4ixztw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933796/tg-products/hvt9ykb7wv9vwn2fegto.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773934457/tg-products/ltj8m2vwgmhol94h9ood.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933932/tg-products/ko7czxgykv0usognjmff.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933933/tg-products/bnlf6iyyg9u6mlqciplj.jpg</t>
+  </si>
+  <si>
+    <t>₽+E116</t>
   </si>
 </sst>
 </file>
@@ -4375,25 +4372,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D80" s="8">
-        <v>12000</v>
+        <v>80000</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>20</v>
@@ -4405,7 +4402,7 @@
         <v>30</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="M80" s="10">
         <v>46100</v>
@@ -4416,7 +4413,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>48</v>
@@ -4434,7 +4431,7 @@
         <v>70</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>20</v>
@@ -4446,7 +4443,7 @@
         <v>87</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M81" s="10">
         <v>46100</v>
@@ -4457,7 +4454,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>48</v>
@@ -4475,7 +4472,7 @@
         <v>70</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>20</v>
@@ -4484,10 +4481,10 @@
         <v>21</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M82" s="10">
         <v>46100</v>
@@ -4498,7 +4495,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>48</v>
@@ -4516,7 +4513,7 @@
         <v>70</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>20</v>
@@ -4528,7 +4525,7 @@
         <v>130</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M83" s="10">
         <v>46100</v>
@@ -4539,7 +4536,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>48</v>
@@ -4557,7 +4554,7 @@
         <v>70</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>20</v>
@@ -4569,7 +4566,7 @@
         <v>30</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M84" s="10">
         <v>46100</v>
@@ -4580,7 +4577,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>48</v>
@@ -4598,7 +4595,7 @@
         <v>70</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>20</v>
@@ -4610,7 +4607,7 @@
         <v>85</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M85" s="10">
         <v>46100</v>
@@ -4621,7 +4618,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>48</v>
@@ -4633,13 +4630,13 @@
         <v>16</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>70</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>20</v>
@@ -4651,7 +4648,7 @@
         <v>41</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M86" s="10">
         <v>46100</v>
@@ -4662,7 +4659,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>48</v>
@@ -4680,7 +4677,7 @@
         <v>70</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>20</v>
@@ -4692,7 +4689,7 @@
         <v>30</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M87" s="10">
         <v>46100</v>
@@ -4703,7 +4700,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>64</v>
@@ -4721,7 +4718,7 @@
         <v>70</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>20</v>
@@ -4733,7 +4730,7 @@
         <v>87</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M88" s="10">
         <v>46100</v>
@@ -4744,7 +4741,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>64</v>
@@ -4756,13 +4753,13 @@
         <v>16</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>70</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>20</v>
@@ -4774,7 +4771,7 @@
         <v>87</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M89" s="10">
         <v>46100</v>
@@ -4785,7 +4782,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>64</v>
@@ -4803,7 +4800,7 @@
         <v>70</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>20</v>
@@ -4815,7 +4812,7 @@
         <v>85</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M90" s="10">
         <v>46100</v>
@@ -4826,7 +4823,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>64</v>
@@ -4844,7 +4841,7 @@
         <v>70</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>20</v>
@@ -4856,7 +4853,7 @@
         <v>87</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M91" s="10">
         <v>46100</v>
@@ -4867,13 +4864,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D92" s="8">
-        <v>49000</v>
+        <v>80000</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>16</v>
@@ -4884,8 +4881,8 @@
       <c r="G92" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H92" s="8" t="s">
-        <v>254</v>
+      <c r="H92" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>20</v>
@@ -4894,10 +4891,10 @@
         <v>21</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="M92" s="10">
         <v>46100</v>
@@ -4908,7 +4905,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>64</v>
@@ -4926,7 +4923,7 @@
         <v>70</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>20</v>
@@ -4938,7 +4935,7 @@
         <v>87</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M93" s="10">
         <v>46100</v>
@@ -4949,16 +4946,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D94" s="8">
         <v>17000</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>17</v>
@@ -4966,8 +4963,8 @@
       <c r="G94" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H94" s="8" t="s">
-        <v>213</v>
+      <c r="H94" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>20</v>
@@ -4990,10 +4987,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D95" s="8">
         <v>25000</v>
@@ -5007,8 +5004,8 @@
       <c r="G95" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H95" s="8" t="s">
-        <v>215</v>
+      <c r="H95" s="11" t="s">
+        <v>250</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>20</v>
@@ -5031,7 +5028,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>89</v>
@@ -5043,13 +5040,13 @@
         <v>16</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>20</v>
@@ -5072,7 +5069,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>60</v>
@@ -5090,7 +5087,7 @@
         <v>18</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>20</v>
@@ -5131,7 +5128,7 @@
         <v>18</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>20</v>
@@ -5154,10 +5151,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D99" s="8">
         <v>40000</v>
@@ -5171,8 +5168,8 @@
       <c r="G99" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H99" s="8" t="s">
-        <v>223</v>
+      <c r="H99" s="11" t="s">
+        <v>251</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>20</v>
@@ -5195,7 +5192,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>141</v>
@@ -5213,7 +5210,7 @@
         <v>90</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>20</v>
@@ -5236,7 +5233,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>141</v>
@@ -5254,7 +5251,7 @@
         <v>90</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I101" s="8" t="s">
         <v>20</v>
@@ -5277,7 +5274,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>141</v>
@@ -5295,7 +5292,7 @@
         <v>90</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I102" s="8" t="s">
         <v>20</v>
@@ -5318,7 +5315,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>141</v>
@@ -5336,7 +5333,7 @@
         <v>90</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I103" s="8" t="s">
         <v>20</v>
@@ -5359,7 +5356,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>48</v>
@@ -5377,7 +5374,7 @@
         <v>90</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>20</v>
@@ -5400,7 +5397,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>48</v>
@@ -5418,7 +5415,7 @@
         <v>90</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>20</v>
@@ -5441,7 +5438,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>48</v>
@@ -5459,7 +5456,7 @@
         <v>90</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I106" s="8" t="s">
         <v>20</v>
@@ -5482,7 +5479,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>48</v>
@@ -5494,13 +5491,13 @@
         <v>16</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>90</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I107" s="8" t="s">
         <v>20</v>
@@ -5523,7 +5520,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>48</v>
@@ -5535,13 +5532,13 @@
         <v>16</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>90</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I108" s="8" t="s">
         <v>20</v>
@@ -5564,7 +5561,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>48</v>
@@ -5582,7 +5579,7 @@
         <v>70</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I109" s="8" t="s">
         <v>20</v>
@@ -5594,7 +5591,7 @@
         <v>130</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M109" s="10">
         <v>46100</v>
@@ -5605,7 +5602,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>48</v>
@@ -5623,7 +5620,7 @@
         <v>70</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I110" s="8" t="s">
         <v>20</v>
@@ -5635,7 +5632,7 @@
         <v>85</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M110" s="10">
         <v>46100</v>
@@ -5646,7 +5643,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>48</v>
@@ -5664,7 +5661,7 @@
         <v>70</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I111" s="8" t="s">
         <v>20</v>
@@ -5676,93 +5673,41 @@
         <v>96</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M111" s="10">
         <v>46100</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="1">
-        <v>111</v>
-      </c>
-      <c r="B112" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D112" s="8">
-        <v>80000</v>
-      </c>
-      <c r="E112" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H112" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="I112" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K112" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L112" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="M112" s="10">
-        <v>46100</v>
-      </c>
+      <c r="A112" s="1"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+      <c r="M112" s="10"/>
     </row>
     <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="1">
-        <v>112</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D113" s="8">
-        <v>80000</v>
-      </c>
-      <c r="E113" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H113" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K113" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L113" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="M113" s="10">
-        <v>46100</v>
-      </c>
+      <c r="A113" s="1"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="10"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B114" s="8"/>
@@ -6289,21 +6234,23 @@
     <hyperlink ref="H77" r:id="rId73" xr:uid="{57F780E1-013A-B44B-A78A-8E13971240FA}"/>
     <hyperlink ref="H78" r:id="rId74" xr:uid="{1FD5469F-F1A8-C74A-AF18-780AB15ADA48}"/>
     <hyperlink ref="H79" r:id="rId75" xr:uid="{FDA055D6-AEAC-A848-86A9-941A9B5E6677}"/>
-    <hyperlink ref="H80" r:id="rId76" xr:uid="{7977804C-3A1F-EB43-AC0B-2A16CC437FED}"/>
-    <hyperlink ref="H100" r:id="rId77" xr:uid="{F6A44307-984E-9E4A-BB29-2096E232D52E}"/>
-    <hyperlink ref="H101" r:id="rId78" xr:uid="{BBB7AEA8-A3E7-2540-9D64-555CF198F0AE}"/>
-    <hyperlink ref="H102" r:id="rId79" xr:uid="{31638D57-F9A1-8440-8AAA-FB7EC3275284}"/>
-    <hyperlink ref="H103" r:id="rId80" xr:uid="{4D67B34A-C716-1048-B21D-FD65FA1FC86A}"/>
-    <hyperlink ref="H104" r:id="rId81" xr:uid="{4F9974E9-281F-324B-B2B6-DB64B7988717}"/>
-    <hyperlink ref="H105" r:id="rId82" xr:uid="{790876C7-43B0-1641-9648-4DA5B66C4E6A}"/>
-    <hyperlink ref="H106" r:id="rId83" xr:uid="{D645509F-DAD4-1B48-AE27-1756FF478CC6}"/>
-    <hyperlink ref="H107" r:id="rId84" xr:uid="{329E350C-1CF8-5C45-95C6-4C3E372F91C2}"/>
-    <hyperlink ref="H108" r:id="rId85" xr:uid="{469EFC21-E4CF-EA44-97D3-E3BC30FBA948}"/>
-    <hyperlink ref="H109" r:id="rId86" xr:uid="{6F4FFC68-88CD-BF45-B17F-2DF461BC021E}"/>
-    <hyperlink ref="H110" r:id="rId87" xr:uid="{234BD536-ADCB-C642-AC40-BC68C8BC75ED}"/>
-    <hyperlink ref="H111" r:id="rId88" xr:uid="{0F913E7E-15FD-6443-9176-9E98916E93F7}"/>
-    <hyperlink ref="H112" r:id="rId89" xr:uid="{7560FF78-E43C-8F41-8F50-98A5F3538B83}"/>
-    <hyperlink ref="H113" r:id="rId90" xr:uid="{97F9E249-BE09-A44A-9460-BA5D56C0AF7D}"/>
+    <hyperlink ref="H100" r:id="rId76" xr:uid="{F6A44307-984E-9E4A-BB29-2096E232D52E}"/>
+    <hyperlink ref="H101" r:id="rId77" xr:uid="{BBB7AEA8-A3E7-2540-9D64-555CF198F0AE}"/>
+    <hyperlink ref="H102" r:id="rId78" xr:uid="{31638D57-F9A1-8440-8AAA-FB7EC3275284}"/>
+    <hyperlink ref="H103" r:id="rId79" xr:uid="{4D67B34A-C716-1048-B21D-FD65FA1FC86A}"/>
+    <hyperlink ref="H104" r:id="rId80" xr:uid="{4F9974E9-281F-324B-B2B6-DB64B7988717}"/>
+    <hyperlink ref="H105" r:id="rId81" xr:uid="{790876C7-43B0-1641-9648-4DA5B66C4E6A}"/>
+    <hyperlink ref="H106" r:id="rId82" xr:uid="{D645509F-DAD4-1B48-AE27-1756FF478CC6}"/>
+    <hyperlink ref="H107" r:id="rId83" xr:uid="{329E350C-1CF8-5C45-95C6-4C3E372F91C2}"/>
+    <hyperlink ref="H108" r:id="rId84" xr:uid="{469EFC21-E4CF-EA44-97D3-E3BC30FBA948}"/>
+    <hyperlink ref="H109" r:id="rId85" xr:uid="{6F4FFC68-88CD-BF45-B17F-2DF461BC021E}"/>
+    <hyperlink ref="H110" r:id="rId86" xr:uid="{234BD536-ADCB-C642-AC40-BC68C8BC75ED}"/>
+    <hyperlink ref="H111" r:id="rId87" xr:uid="{0F913E7E-15FD-6443-9176-9E98916E93F7}"/>
+    <hyperlink ref="H94" r:id="rId88" xr:uid="{02E7DD7A-B547-6244-A2A1-E756539494E9}"/>
+    <hyperlink ref="H95" r:id="rId89" xr:uid="{14B32940-312C-6B49-98C8-25110195771A}"/>
+    <hyperlink ref="H99" r:id="rId90" xr:uid="{FB8A849A-02BC-804A-B3EF-635EB1A65166}"/>
+    <hyperlink ref="H92" r:id="rId91" xr:uid="{65A68C2D-B57A-9B49-95D7-A2B95A5E4A2B}"/>
+    <hyperlink ref="H80" r:id="rId92" xr:uid="{67990DD2-B01E-3C4F-8FDD-D08E451508D9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCBA49C-6C8A-2249-AAC7-D26080679A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E52298-3149-6C49-A045-21F62CDF33FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="313">
   <si>
     <t>id</t>
   </si>
@@ -157,9 +157,6 @@
     <t>Футболка Louis Vuitton</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>14000</t>
   </si>
   <si>
@@ -781,7 +778,187 @@
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933932/tg-products/ko7czxgykv0usognjmff.jpg, https://res.cloudinary.com/dlexrnrhe/image/upload/v1773933933/tg-products/bnlf6iyyg9u6mlqciplj.jpg</t>
   </si>
   <si>
-    <t>₽+E116</t>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368075/tg-products/r9hmtnaus6d861qwxlvc.jpg</t>
+  </si>
+  <si>
+    <t>Кофта Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368078/tg-products/gltlvmzizsuvyt4td4xc.jpg</t>
+  </si>
+  <si>
+    <t>Сумка Bottega Veneta Pinacoteca</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368081/tg-products/vbpwsf57ndhh3kkvrww3.jpg</t>
+  </si>
+  <si>
+    <t>24*15*12 см</t>
+  </si>
+  <si>
+    <t>Куртка Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368083/tg-products/dvoayehprgatamloqiff.jpg</t>
+  </si>
+  <si>
+    <t>Лонгслив Chanel</t>
+  </si>
+  <si>
+    <t>Материал кашемир и шелк</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368085/tg-products/iqpvcafk3cxovg3ljkii.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368088/tg-products/q8ik0oisqtlbpztx11do.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368091/tg-products/i7c5hhjufb6udolqnlaw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368094/tg-products/f56fthfhtjuxswgbxmdp.jpg</t>
+  </si>
+  <si>
+    <t>Куртка YSL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368096/tg-products/orcffpudflq6cpt5uiin.jpg</t>
+  </si>
+  <si>
+    <t>оранжевы</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368099/tg-products/syqewsso4wbnjqdoozsb.jpg</t>
+  </si>
+  <si>
+    <t>Сумка YSL Niki Shopping</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368101/tg-products/zuu8gtyv0rt1d2mg7nb5.jpg</t>
+  </si>
+  <si>
+    <t>25*19*10 см</t>
+  </si>
+  <si>
+    <t>Сапоги Celine Riley</t>
+  </si>
+  <si>
+    <t>Материал Каучук и техническая ткань</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368104/tg-products/mn1wf2frtzdthypjz606.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368106/tg-products/evtcdxh9tsl48u6ecwg3.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368108/tg-products/qg4artwluc7kgpyq2vav.jpg</t>
+  </si>
+  <si>
+    <t>37*33*14 см</t>
+  </si>
+  <si>
+    <t>Кардиган Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368111/tg-products/rtfxxkbruhixd05s5hiy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368114/tg-products/oyhtylshhghb41kasafa.jpg</t>
+  </si>
+  <si>
+    <t>Трикотажная футболка Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368116/tg-products/oo2mtzoojxk5mooxnd5z.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368119/tg-products/eh5vvmpow0rmskdsdfut.jpg</t>
+  </si>
+  <si>
+    <t>Поло Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368121/tg-products/d1sqv2ubyxsw4sm53riw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368124/tg-products/beahhvod1zi8tqpo64z7.jpg</t>
+  </si>
+  <si>
+    <t>Майка YSL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368126/tg-products/fzfq0tamiglwxdkj6qfx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368128/tg-products/z0oi5tb2pf0nvnjumq5r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368131/tg-products/cid4ed5domt6yuthkhqt.jpg</t>
+  </si>
+  <si>
+    <t>Платье Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368133/tg-products/giipoicsax2ullym73jf.jpg</t>
+  </si>
+  <si>
+    <t>Тренч Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368136/tg-products/iyu9ruxrsyjvk15m0r8h.jpg</t>
+  </si>
+  <si>
+    <t>Футболка Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368138/tg-products/jzgrzcvx65cph6j1umr9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368141/tg-products/nrza5omtyzr0zdl8nhu0.jpg</t>
+  </si>
+  <si>
+    <t>Шорты Louis Vuitton</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368143/tg-products/viseso5uyka6gdsuhe6j.jpg</t>
+  </si>
+  <si>
+    <t>Платье Miumiu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368146/tg-products/ikr1xryp8fczjhx9rlqo.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368148/tg-products/q9bye4bbsuef95nztohu.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368152/tg-products/mk14rypfsye9gfuqy0nq.jpg</t>
+  </si>
+  <si>
+    <t>Майка Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368155/tg-products/sc6vnkdawotlo54o8rws.jpg</t>
+  </si>
+  <si>
+    <t>Рубашка Louis Vuitton</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368157/tg-products/phosfcyl1yhwexzw7j2n.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368595/tg-products/ax4vbpox4vqujimqeylg.jpg</t>
+  </si>
+  <si>
+    <t>Лонгслив Prada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368598/tg-products/vpe2ko1djhicxbirrfkv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368601/tg-products/mh1sazndcavrnpsenrvi.jpg</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1302,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1315,7 +1492,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -1397,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -1438,7 +1615,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>20</v>
@@ -1479,7 +1656,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>20</v>
@@ -1504,11 +1681,11 @@
       <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
@@ -1520,7 +1697,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>20</v>
@@ -1543,25 +1720,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>20</v>
@@ -1584,25 +1761,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>20</v>
@@ -1625,10 +1802,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -1643,7 +1820,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>20</v>
@@ -1666,10 +1843,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -1684,7 +1861,7 @@
         <v>18</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>20</v>
@@ -1725,7 +1902,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>20</v>
@@ -1748,13 +1925,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>16</v>
@@ -1766,7 +1943,7 @@
         <v>18</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>20</v>
@@ -1789,10 +1966,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>32</v>
@@ -1807,7 +1984,7 @@
         <v>18</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>20</v>
@@ -1830,10 +2007,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>32</v>
@@ -1842,13 +2019,13 @@
         <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>20</v>
@@ -1871,25 +2048,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>20</v>
@@ -1912,13 +2089,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -1930,7 +2107,7 @@
         <v>18</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>20</v>
@@ -1953,10 +2130,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>15</v>
@@ -1971,7 +2148,7 @@
         <v>18</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>20</v>
@@ -1994,37 +2171,37 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="H22" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M22" s="10">
         <v>46099</v>
@@ -2035,25 +2212,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>75</v>
-      </c>
       <c r="G23" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>20</v>
@@ -2076,13 +2253,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>16</v>
@@ -2094,7 +2271,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>20</v>
@@ -2117,10 +2294,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8">
         <v>13000</v>
@@ -2135,7 +2312,7 @@
         <v>18</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>20</v>
@@ -2158,10 +2335,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="8">
         <v>13000</v>
@@ -2176,7 +2353,7 @@
         <v>18</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>20</v>
@@ -2185,7 +2362,7 @@
         <v>21</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>23</v>
@@ -2199,10 +2376,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="8">
         <v>19000</v>
@@ -2217,7 +2394,7 @@
         <v>18</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>20</v>
@@ -2240,10 +2417,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="D28" s="8">
         <v>18000</v>
@@ -2252,13 +2429,13 @@
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>20</v>
@@ -2281,7 +2458,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>37</v>
@@ -2299,7 +2476,7 @@
         <v>18</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>20</v>
@@ -2322,10 +2499,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D30" s="8">
         <v>19000</v>
@@ -2340,7 +2517,7 @@
         <v>18</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>20</v>
@@ -2349,7 +2526,7 @@
         <v>21</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>23</v>
@@ -2363,10 +2540,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D31" s="8">
         <v>32000</v>
@@ -2375,13 +2552,13 @@
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>20</v>
@@ -2404,10 +2581,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32" s="8">
         <v>28000</v>
@@ -2416,13 +2593,13 @@
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>20</v>
@@ -2431,7 +2608,7 @@
         <v>21</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>23</v>
@@ -2445,10 +2622,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D33" s="8">
         <v>21000</v>
@@ -2457,25 +2634,25 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="M33" s="10">
         <v>46099</v>
@@ -2486,10 +2663,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D34" s="8">
         <v>24000</v>
@@ -2498,13 +2675,13 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>20</v>
@@ -2516,7 +2693,7 @@
         <v>41</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M34" s="10">
         <v>46099</v>
@@ -2527,10 +2704,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D35" s="8">
         <v>24000</v>
@@ -2539,13 +2716,13 @@
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>20</v>
@@ -2557,7 +2734,7 @@
         <v>22</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M35" s="10">
         <v>46099</v>
@@ -2568,10 +2745,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D36" s="8">
         <v>24000</v>
@@ -2580,25 +2757,25 @@
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H36" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="L36" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M36" s="10">
         <v>46099</v>
@@ -2609,10 +2786,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D37" s="8">
         <v>24000</v>
@@ -2621,13 +2798,13 @@
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>20</v>
@@ -2636,10 +2813,10 @@
         <v>21</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M37" s="10">
         <v>46099</v>
@@ -2650,10 +2827,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D38" s="8">
         <v>24000</v>
@@ -2662,13 +2839,13 @@
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>20</v>
@@ -2677,10 +2854,10 @@
         <v>21</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M38" s="10">
         <v>46099</v>
@@ -2691,10 +2868,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="8">
         <v>24000</v>
@@ -2703,13 +2880,13 @@
         <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>20</v>
@@ -2721,7 +2898,7 @@
         <v>30</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M39" s="10">
         <v>46099</v>
@@ -2732,10 +2909,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D40" s="8">
         <v>24000</v>
@@ -2744,13 +2921,13 @@
         <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>20</v>
@@ -2759,10 +2936,10 @@
         <v>21</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M40" s="10">
         <v>46099</v>
@@ -2773,10 +2950,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D41" s="8">
         <v>24000</v>
@@ -2785,13 +2962,13 @@
         <v>16</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>20</v>
@@ -2803,7 +2980,7 @@
         <v>26</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M41" s="10">
         <v>46099</v>
@@ -2814,10 +2991,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D42" s="8">
         <v>24000</v>
@@ -2826,13 +3003,13 @@
         <v>16</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>20</v>
@@ -2841,10 +3018,10 @@
         <v>21</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M42" s="10">
         <v>46099</v>
@@ -2855,10 +3032,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" s="8">
         <v>24000</v>
@@ -2867,13 +3044,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>20</v>
@@ -2882,10 +3059,10 @@
         <v>21</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M43" s="10">
         <v>46099</v>
@@ -2896,10 +3073,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" s="8">
         <v>24000</v>
@@ -2908,13 +3085,13 @@
         <v>16</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>20</v>
@@ -2923,10 +3100,10 @@
         <v>21</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M44" s="10">
         <v>46099</v>
@@ -2937,10 +3114,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D45" s="8">
         <v>27000</v>
@@ -2949,13 +3126,13 @@
         <v>16</v>
       </c>
       <c r="F45" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H45" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>20</v>
@@ -2967,7 +3144,7 @@
         <v>22</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M45" s="10">
         <v>46099</v>
@@ -2978,10 +3155,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D46" s="8">
         <v>27000</v>
@@ -2990,13 +3167,13 @@
         <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>20</v>
@@ -3005,10 +3182,10 @@
         <v>21</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M46" s="10">
         <v>46099</v>
@@ -3019,10 +3196,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D47" s="8">
         <v>20000</v>
@@ -3031,13 +3208,13 @@
         <v>16</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>20</v>
@@ -3049,7 +3226,7 @@
         <v>26</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M47" s="10">
         <v>46099</v>
@@ -3060,10 +3237,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="8">
         <v>20000</v>
@@ -3072,13 +3249,13 @@
         <v>16</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>20</v>
@@ -3087,10 +3264,10 @@
         <v>21</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M48" s="10">
         <v>46099</v>
@@ -3101,10 +3278,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D49" s="8">
         <v>20000</v>
@@ -3113,13 +3290,13 @@
         <v>16</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>20</v>
@@ -3128,10 +3305,10 @@
         <v>21</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M49" s="10">
         <v>46099</v>
@@ -3142,10 +3319,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" s="8">
         <v>55000</v>
@@ -3154,25 +3331,25 @@
         <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H50" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="M50" s="10">
         <v>46099</v>
@@ -3183,10 +3360,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D51" s="8">
         <v>55000</v>
@@ -3195,13 +3372,13 @@
         <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>20</v>
@@ -3210,10 +3387,10 @@
         <v>21</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M51" s="10">
         <v>46099</v>
@@ -3224,10 +3401,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52" s="8">
         <v>55000</v>
@@ -3236,13 +3413,13 @@
         <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>20</v>
@@ -3251,10 +3428,10 @@
         <v>21</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M52" s="10">
         <v>46099</v>
@@ -3265,10 +3442,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D53" s="8">
         <v>65000</v>
@@ -3277,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>20</v>
@@ -3295,7 +3472,7 @@
         <v>22</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M53" s="10">
         <v>46099</v>
@@ -3306,10 +3483,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="D54" s="8">
         <v>60000</v>
@@ -3318,13 +3495,13 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>20</v>
@@ -3333,10 +3510,10 @@
         <v>21</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M54" s="10">
         <v>46099</v>
@@ -3347,10 +3524,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="D55" s="8">
         <v>60000</v>
@@ -3359,13 +3536,13 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>20</v>
@@ -3374,10 +3551,10 @@
         <v>21</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M55" s="10">
         <v>46099</v>
@@ -3388,10 +3565,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>126</v>
       </c>
       <c r="D56" s="8">
         <v>60000</v>
@@ -3400,13 +3577,13 @@
         <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>20</v>
@@ -3415,10 +3592,10 @@
         <v>21</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M56" s="10">
         <v>46099</v>
@@ -3429,10 +3606,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="8">
         <v>55000</v>
@@ -3441,13 +3618,13 @@
         <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>20</v>
@@ -3456,10 +3633,10 @@
         <v>21</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M57" s="10">
         <v>46099</v>
@@ -3470,10 +3647,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" s="8">
         <v>64000</v>
@@ -3482,13 +3659,13 @@
         <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I58" s="8" t="s">
         <v>20</v>
@@ -3500,7 +3677,7 @@
         <v>22</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M58" s="10">
         <v>46099</v>
@@ -3511,10 +3688,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D59" s="8">
         <v>64000</v>
@@ -3523,25 +3700,25 @@
         <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="H59" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H59" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="L59" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M59" s="10">
         <v>46099</v>
@@ -3552,10 +3729,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60" s="8">
         <v>64000</v>
@@ -3564,13 +3741,13 @@
         <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G60" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G60" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H60" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>20</v>
@@ -3579,10 +3756,10 @@
         <v>21</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M60" s="10">
         <v>46099</v>
@@ -3593,10 +3770,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61" s="8">
         <v>64000</v>
@@ -3605,13 +3782,13 @@
         <v>16</v>
       </c>
       <c r="F61" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G61" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H61" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>20</v>
@@ -3620,10 +3797,10 @@
         <v>21</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M61" s="10">
         <v>46099</v>
@@ -3634,10 +3811,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D62" s="8">
         <v>36000</v>
@@ -3646,13 +3823,13 @@
         <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H62" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>20</v>
@@ -3661,10 +3838,10 @@
         <v>21</v>
       </c>
       <c r="K62" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="L62" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="L62" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="M62" s="10">
         <v>46099</v>
@@ -3675,10 +3852,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D63" s="8">
         <v>36000</v>
@@ -3687,13 +3864,13 @@
         <v>16</v>
       </c>
       <c r="F63" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G63" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H63" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>20</v>
@@ -3702,10 +3879,10 @@
         <v>21</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M63" s="10">
         <v>46099</v>
@@ -3716,10 +3893,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64" s="8">
         <v>36000</v>
@@ -3728,25 +3905,25 @@
         <v>16</v>
       </c>
       <c r="F64" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G64" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="H64" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H64" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="L64" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M64" s="10">
         <v>46099</v>
@@ -3757,10 +3934,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D65" s="8">
         <v>36000</v>
@@ -3769,13 +3946,13 @@
         <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G65" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H65" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>20</v>
@@ -3784,10 +3961,10 @@
         <v>21</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M65" s="10">
         <v>46099</v>
@@ -3798,10 +3975,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D66" s="8">
         <v>36000</v>
@@ -3810,13 +3987,13 @@
         <v>16</v>
       </c>
       <c r="F66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H66" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>20</v>
@@ -3825,10 +4002,10 @@
         <v>21</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M66" s="10">
         <v>46099</v>
@@ -3839,10 +4016,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D67" s="8">
         <v>21000</v>
@@ -3851,13 +4028,13 @@
         <v>16</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>20</v>
@@ -3869,7 +4046,7 @@
         <v>26</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M67" s="10">
         <v>46099</v>
@@ -3880,10 +4057,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D68" s="8">
         <v>21000</v>
@@ -3892,13 +4069,13 @@
         <v>16</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I68" s="8" t="s">
         <v>20</v>
@@ -3910,7 +4087,7 @@
         <v>26</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M68" s="10">
         <v>46099</v>
@@ -3921,10 +4098,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="8">
         <v>32000</v>
@@ -3933,13 +4110,13 @@
         <v>16</v>
       </c>
       <c r="F69" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H69" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>20</v>
@@ -3951,7 +4128,7 @@
         <v>41</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M69" s="10">
         <v>46099</v>
@@ -3962,10 +4139,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D70" s="8">
         <v>63000</v>
@@ -3974,14 +4151,14 @@
         <v>16</v>
       </c>
       <c r="F70" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="I70" s="8" t="s">
         <v>20</v>
       </c>
@@ -3989,10 +4166,10 @@
         <v>21</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M70" s="10">
         <v>46099</v>
@@ -4003,10 +4180,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D71" s="8">
         <v>36000</v>
@@ -4015,13 +4192,13 @@
         <v>16</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>20</v>
@@ -4033,7 +4210,7 @@
         <v>22</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M71" s="10">
         <v>46099</v>
@@ -4044,10 +4221,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" s="8">
         <v>36000</v>
@@ -4056,13 +4233,13 @@
         <v>16</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>20</v>
@@ -4074,7 +4251,7 @@
         <v>22</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M72" s="10">
         <v>46099</v>
@@ -4085,10 +4262,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>141</v>
       </c>
       <c r="D73" s="8">
         <v>25000</v>
@@ -4097,13 +4274,13 @@
         <v>16</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>20</v>
@@ -4115,7 +4292,7 @@
         <v>22</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M73" s="10">
         <v>46099</v>
@@ -4126,10 +4303,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D74" s="8">
         <v>12000</v>
@@ -4144,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I74" s="8" t="s">
         <v>20</v>
@@ -4153,10 +4330,10 @@
         <v>21</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M74" s="10">
         <v>46100</v>
@@ -4167,7 +4344,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>14</v>
@@ -4185,7 +4362,7 @@
         <v>18</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I75" s="8" t="s">
         <v>20</v>
@@ -4197,7 +4374,7 @@
         <v>26</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M75" s="10">
         <v>46100</v>
@@ -4208,10 +4385,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D76" s="8">
         <v>12000</v>
@@ -4226,7 +4403,7 @@
         <v>18</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I76" s="8" t="s">
         <v>20</v>
@@ -4235,10 +4412,10 @@
         <v>21</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M76" s="10">
         <v>46100</v>
@@ -4267,7 +4444,7 @@
         <v>18</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>20</v>
@@ -4279,7 +4456,7 @@
         <v>30</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M77" s="10">
         <v>46100</v>
@@ -4290,10 +4467,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D78" s="8">
         <v>13000</v>
@@ -4308,7 +4485,7 @@
         <v>18</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I78" s="8" t="s">
         <v>20</v>
@@ -4320,7 +4497,7 @@
         <v>26</v>
       </c>
       <c r="L78" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M78" s="10">
         <v>46100</v>
@@ -4331,10 +4508,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D79" s="8">
         <v>11000</v>
@@ -4349,7 +4526,7 @@
         <v>18</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>20</v>
@@ -4361,7 +4538,7 @@
         <v>41</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M79" s="10">
         <v>46100</v>
@@ -4372,10 +4549,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D80" s="8">
         <v>80000</v>
@@ -4384,13 +4561,13 @@
         <v>16</v>
       </c>
       <c r="F80" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G80" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G80" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H80" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>20</v>
@@ -4402,7 +4579,7 @@
         <v>30</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M80" s="10">
         <v>46100</v>
@@ -4413,10 +4590,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D81" s="8">
         <v>80000</v>
@@ -4425,13 +4602,13 @@
         <v>16</v>
       </c>
       <c r="F81" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G81" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G81" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H81" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>20</v>
@@ -4440,10 +4617,10 @@
         <v>21</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M81" s="10">
         <v>46100</v>
@@ -4454,10 +4631,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D82" s="8">
         <v>80000</v>
@@ -4466,13 +4643,13 @@
         <v>16</v>
       </c>
       <c r="F82" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G82" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G82" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H82" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>20</v>
@@ -4481,10 +4658,10 @@
         <v>21</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M82" s="10">
         <v>46100</v>
@@ -4495,10 +4672,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D83" s="8">
         <v>68000</v>
@@ -4507,25 +4684,25 @@
         <v>16</v>
       </c>
       <c r="F83" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H83" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L83" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K83" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="L83" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="M83" s="10">
         <v>46100</v>
@@ -4536,10 +4713,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D84" s="8">
         <v>80000</v>
@@ -4548,13 +4725,13 @@
         <v>16</v>
       </c>
       <c r="F84" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G84" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H84" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>20</v>
@@ -4566,7 +4743,7 @@
         <v>30</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M84" s="10">
         <v>46100</v>
@@ -4577,10 +4754,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D85" s="8">
         <v>80000</v>
@@ -4589,13 +4766,13 @@
         <v>16</v>
       </c>
       <c r="F85" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G85" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H85" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>20</v>
@@ -4604,10 +4781,10 @@
         <v>21</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M85" s="10">
         <v>46100</v>
@@ -4618,10 +4795,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D86" s="8">
         <v>80000</v>
@@ -4630,13 +4807,13 @@
         <v>16</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I86" s="8" t="s">
         <v>20</v>
@@ -4648,7 +4825,7 @@
         <v>41</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M86" s="10">
         <v>46100</v>
@@ -4659,10 +4836,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D87" s="8">
         <v>80000</v>
@@ -4671,13 +4848,13 @@
         <v>16</v>
       </c>
       <c r="F87" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G87" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G87" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H87" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>20</v>
@@ -4689,7 +4866,7 @@
         <v>30</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M87" s="10">
         <v>46100</v>
@@ -4700,10 +4877,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D88" s="8">
         <v>56000</v>
@@ -4712,13 +4889,13 @@
         <v>16</v>
       </c>
       <c r="F88" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H88" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I88" s="8" t="s">
         <v>20</v>
@@ -4727,10 +4904,10 @@
         <v>21</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M88" s="10">
         <v>46100</v>
@@ -4741,10 +4918,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D89" s="8">
         <v>56000</v>
@@ -4753,14 +4930,14 @@
         <v>16</v>
       </c>
       <c r="F89" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H89" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="I89" s="8" t="s">
         <v>20</v>
       </c>
@@ -4768,10 +4945,10 @@
         <v>21</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M89" s="10">
         <v>46100</v>
@@ -4782,10 +4959,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D90" s="8">
         <v>54000</v>
@@ -4794,25 +4971,25 @@
         <v>16</v>
       </c>
       <c r="F90" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G90" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G90" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H90" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L90" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K90" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L90" s="8" t="s">
-        <v>207</v>
       </c>
       <c r="M90" s="10">
         <v>46100</v>
@@ -4823,10 +5000,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D91" s="8">
         <v>54000</v>
@@ -4835,13 +5012,13 @@
         <v>16</v>
       </c>
       <c r="F91" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G91" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G91" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H91" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I91" s="8" t="s">
         <v>20</v>
@@ -4850,10 +5027,10 @@
         <v>21</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M91" s="10">
         <v>46100</v>
@@ -4864,10 +5041,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D92" s="8">
         <v>80000</v>
@@ -4876,13 +5053,13 @@
         <v>16</v>
       </c>
       <c r="F92" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G92" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G92" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H92" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>20</v>
@@ -4894,7 +5071,7 @@
         <v>26</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M92" s="10">
         <v>46100</v>
@@ -4905,10 +5082,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D93" s="8">
         <v>49000</v>
@@ -4917,13 +5094,13 @@
         <v>16</v>
       </c>
       <c r="F93" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G93" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G93" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H93" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>20</v>
@@ -4932,10 +5109,10 @@
         <v>21</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M93" s="10">
         <v>46100</v>
@@ -4946,16 +5123,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D94" s="8">
         <v>17000</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>253</v>
+        <v>16</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>17</v>
@@ -4964,7 +5141,7 @@
         <v>18</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>20</v>
@@ -4976,7 +5153,7 @@
         <v>41</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M94" s="10">
         <v>46100</v>
@@ -4987,10 +5164,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D95" s="8">
         <v>25000</v>
@@ -4999,13 +5176,13 @@
         <v>16</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>20</v>
@@ -5017,7 +5194,7 @@
         <v>26</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M95" s="10">
         <v>46100</v>
@@ -5028,10 +5205,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D96" s="8">
         <v>28000</v>
@@ -5040,13 +5217,13 @@
         <v>16</v>
       </c>
       <c r="F96" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>20</v>
@@ -5058,7 +5235,7 @@
         <v>41</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M96" s="10">
         <v>46100</v>
@@ -5069,10 +5246,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D97" s="8">
         <v>12500</v>
@@ -5087,7 +5264,7 @@
         <v>18</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>20</v>
@@ -5099,7 +5276,7 @@
         <v>30</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M97" s="10">
         <v>46100</v>
@@ -5122,13 +5299,13 @@
         <v>16</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>20</v>
@@ -5137,10 +5314,10 @@
         <v>21</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M98" s="10">
         <v>46100</v>
@@ -5151,10 +5328,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D99" s="8">
         <v>40000</v>
@@ -5163,13 +5340,13 @@
         <v>16</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>18</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>20</v>
@@ -5178,10 +5355,10 @@
         <v>21</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M99" s="10">
         <v>46100</v>
@@ -5192,10 +5369,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="8">
         <v>22000</v>
@@ -5204,13 +5381,13 @@
         <v>16</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>20</v>
@@ -5219,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M100" s="10">
         <v>46100</v>
@@ -5233,10 +5410,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D101" s="8">
         <v>22000</v>
@@ -5245,13 +5422,13 @@
         <v>16</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I101" s="8" t="s">
         <v>20</v>
@@ -5263,7 +5440,7 @@
         <v>41</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M101" s="10">
         <v>46100</v>
@@ -5274,10 +5451,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" s="8">
         <v>22000</v>
@@ -5286,13 +5463,13 @@
         <v>16</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I102" s="8" t="s">
         <v>20</v>
@@ -5304,7 +5481,7 @@
         <v>30</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M102" s="10">
         <v>46100</v>
@@ -5315,10 +5492,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D103" s="8">
         <v>22000</v>
@@ -5327,13 +5504,13 @@
         <v>16</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I103" s="8" t="s">
         <v>20</v>
@@ -5345,7 +5522,7 @@
         <v>22</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M103" s="10">
         <v>46100</v>
@@ -5356,10 +5533,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D104" s="8">
         <v>25000</v>
@@ -5368,13 +5545,13 @@
         <v>16</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>20</v>
@@ -5383,10 +5560,10 @@
         <v>21</v>
       </c>
       <c r="K104" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L104" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M104" s="10">
         <v>46100</v>
@@ -5397,10 +5574,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D105" s="8">
         <v>25000</v>
@@ -5409,13 +5586,13 @@
         <v>16</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>20</v>
@@ -5424,10 +5601,10 @@
         <v>21</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M105" s="10">
         <v>46100</v>
@@ -5438,10 +5615,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D106" s="8">
         <v>26000</v>
@@ -5450,25 +5627,25 @@
         <v>16</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G106" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K106" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L106" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="H106" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J106" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K106" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="L106" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="M106" s="10">
         <v>46100</v>
@@ -5479,10 +5656,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D107" s="8">
         <v>26000</v>
@@ -5491,25 +5668,25 @@
         <v>16</v>
       </c>
       <c r="F107" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H107" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G107" s="8" t="s">
+      <c r="I107" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L107" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="H107" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="I107" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J107" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K107" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="L107" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="M107" s="10">
         <v>46100</v>
@@ -5520,10 +5697,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D108" s="8">
         <v>26000</v>
@@ -5532,25 +5709,25 @@
         <v>16</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G108" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K108" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L108" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="H108" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J108" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K108" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L108" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="M108" s="10">
         <v>46100</v>
@@ -5561,10 +5738,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D109" s="8">
         <v>80000</v>
@@ -5573,25 +5750,25 @@
         <v>16</v>
       </c>
       <c r="F109" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G109" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G109" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H109" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L109" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="I109" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K109" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="L109" s="8" t="s">
-        <v>234</v>
       </c>
       <c r="M109" s="10">
         <v>46100</v>
@@ -5602,10 +5779,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D110" s="8">
         <v>80000</v>
@@ -5614,13 +5791,13 @@
         <v>16</v>
       </c>
       <c r="F110" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G110" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G110" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H110" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I110" s="8" t="s">
         <v>20</v>
@@ -5629,10 +5806,10 @@
         <v>21</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M110" s="10">
         <v>46100</v>
@@ -5643,10 +5820,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D111" s="8">
         <v>80000</v>
@@ -5655,13 +5832,13 @@
         <v>16</v>
       </c>
       <c r="F111" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G111" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G111" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="H111" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I111" s="8" t="s">
         <v>20</v>
@@ -5670,492 +5847,1480 @@
         <v>21</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M111" s="10">
         <v>46100</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="1"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="11"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="10"/>
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="8">
+        <v>40000</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M112" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="1"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="11"/>
-      <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="10"/>
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D113" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M113" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="8"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="8"/>
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D114" s="8">
+        <v>44000</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="M114" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="8"/>
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D115" s="8">
+        <v>52000</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M115" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
-      <c r="G116" s="8"/>
-      <c r="H116" s="8"/>
-      <c r="I116" s="8"/>
-      <c r="J116" s="8"/>
-      <c r="K116" s="8"/>
-      <c r="L116" s="8"/>
-      <c r="M116" s="8"/>
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D116" s="8">
+        <v>30000</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H116" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M116" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="8"/>
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M117" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="M118" s="8"/>
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M118" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D119" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K119" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M119" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="8"/>
-      <c r="J120" s="8"/>
-      <c r="K120" s="8"/>
-      <c r="L120" s="8"/>
-      <c r="M120" s="8"/>
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D120" s="8">
+        <v>35000</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M120" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="M121" s="8"/>
+      <c r="G121" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K121" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M121" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="8"/>
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D122" s="8">
+        <v>45000</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J122" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L122" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M122" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D123" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M123" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8"/>
-      <c r="L124" s="8"/>
-      <c r="M124" s="8"/>
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D124" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J124" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K124" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M124" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B125" s="8"/>
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="M125" s="8"/>
+      <c r="D125" s="8">
+        <v>54000</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J125" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K125" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="M125" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="8"/>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="8"/>
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" s="8">
+        <v>35000</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K126" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L126" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M126" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K127" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M127" s="10">
+        <v>46117</v>
+      </c>
     </row>
     <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D128" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="8"/>
-      <c r="L128" s="8"/>
-      <c r="M128" s="8"/>
-    </row>
-    <row r="129" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="8"/>
-    </row>
-    <row r="130" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
+      <c r="G128" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M128" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D129" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M129" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="8"/>
-    </row>
-    <row r="131" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
+      <c r="G130" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J130" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K130" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L130" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M130" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
-    </row>
-    <row r="132" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="8"/>
-      <c r="L132" s="8"/>
-      <c r="M132" s="8"/>
-    </row>
-    <row r="133" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="8"/>
-      <c r="I133" s="8"/>
-      <c r="J133" s="8"/>
-      <c r="K133" s="8"/>
-      <c r="L133" s="8"/>
-      <c r="M133" s="8"/>
-    </row>
-    <row r="134" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8"/>
-      <c r="J134" s="8"/>
-      <c r="K134" s="8"/>
-      <c r="L134" s="8"/>
-      <c r="M134" s="8"/>
-    </row>
-    <row r="135" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="8"/>
-      <c r="L135" s="8"/>
-      <c r="M135" s="8"/>
-    </row>
-    <row r="136" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="8"/>
-      <c r="L136" s="8"/>
-      <c r="M136" s="8"/>
-    </row>
-    <row r="137" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="8"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="8"/>
-      <c r="L137" s="8"/>
-      <c r="M137" s="8"/>
-    </row>
-    <row r="138" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="8"/>
-      <c r="I138" s="8"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="8"/>
-      <c r="L138" s="8"/>
-      <c r="M138" s="8"/>
-    </row>
-    <row r="139" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="8"/>
-      <c r="I139" s="8"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="M139" s="8"/>
-    </row>
-    <row r="140" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
-      <c r="H140" s="8"/>
-      <c r="I140" s="8"/>
-      <c r="J140" s="8"/>
-      <c r="K140" s="8"/>
-      <c r="L140" s="8"/>
-      <c r="M140" s="8"/>
-    </row>
-    <row r="141" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="8"/>
-      <c r="H141" s="8"/>
-      <c r="I141" s="8"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="8"/>
-      <c r="L141" s="8"/>
-      <c r="M141" s="8"/>
-    </row>
-    <row r="142" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B142" s="8"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="8"/>
-      <c r="L142" s="8"/>
-      <c r="M142" s="8"/>
-    </row>
-    <row r="143" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="8"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="L143" s="8"/>
-      <c r="M143" s="8"/>
-    </row>
-    <row r="144" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="8"/>
-      <c r="J144" s="8"/>
-      <c r="K144" s="8"/>
-      <c r="L144" s="8"/>
-      <c r="M144" s="8"/>
-    </row>
-    <row r="145" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="8"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-      <c r="M145" s="8"/>
+      <c r="G131" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M131" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J132" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M132" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" s="8">
+        <v>17000</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K133" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L133" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M133" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L134" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M134" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D135" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J135" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K135" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M135" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D136" s="8">
+        <v>49000</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J136" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M136" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D137" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J137" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K137" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L137" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M137" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J138" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K138" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M138" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D139" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J139" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M139" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D140" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J140" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K140" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M140" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" s="8">
+        <v>13000</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I141" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J141" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K141" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M141" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D142" s="8">
+        <v>11000</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J142" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K142" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L142" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M142" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143" s="8">
+        <v>11000</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J143" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K143" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L143" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M143" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D144" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J144" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K144" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L144" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M144" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="8">
+        <v>28000</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J145" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K145" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L145" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M145" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D146" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H146" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J146" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L146" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M146" s="10">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="8">
+        <v>40000</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J147" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K147" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L147" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M147" s="10">
+        <v>46117</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6251,6 +7416,42 @@
     <hyperlink ref="H99" r:id="rId90" xr:uid="{FB8A849A-02BC-804A-B3EF-635EB1A65166}"/>
     <hyperlink ref="H92" r:id="rId91" xr:uid="{65A68C2D-B57A-9B49-95D7-A2B95A5E4A2B}"/>
     <hyperlink ref="H80" r:id="rId92" xr:uid="{67990DD2-B01E-3C4F-8FDD-D08E451508D9}"/>
+    <hyperlink ref="H112" r:id="rId93" xr:uid="{FD76E8B9-7C3D-2148-9EDF-68B4029FB7C3}"/>
+    <hyperlink ref="H113" r:id="rId94" xr:uid="{A28179D6-5ED4-B24D-A02F-3BDCFF601BF0}"/>
+    <hyperlink ref="H114" r:id="rId95" xr:uid="{557D150E-2C3A-204D-9A4D-7447852052D5}"/>
+    <hyperlink ref="H115" r:id="rId96" xr:uid="{495A726F-C676-1B45-A10E-140A818AE786}"/>
+    <hyperlink ref="H116" r:id="rId97" xr:uid="{0E0B0862-90FF-704B-A572-0203B6BD70BA}"/>
+    <hyperlink ref="H117" r:id="rId98" xr:uid="{77AA6BBA-B1E4-8244-9626-302DF9E5B4B6}"/>
+    <hyperlink ref="H118" r:id="rId99" xr:uid="{5E8A39D1-382A-6748-8FF1-CE15D82CC440}"/>
+    <hyperlink ref="H119" r:id="rId100" xr:uid="{6D1591BE-C962-E64E-BAF4-6609DF4FC7D6}"/>
+    <hyperlink ref="H120" r:id="rId101" xr:uid="{254ED1E2-CE9F-BD40-B0A7-86B965BA668B}"/>
+    <hyperlink ref="H121" r:id="rId102" xr:uid="{D013788B-75D1-EE4F-83E1-AD2DA5EB16C6}"/>
+    <hyperlink ref="H122" r:id="rId103" xr:uid="{B291B2B9-7FA6-7449-A529-BE853868A01C}"/>
+    <hyperlink ref="H123" r:id="rId104" xr:uid="{29ED58B4-70AC-6343-B8BA-7F0BE1183F1B}"/>
+    <hyperlink ref="H124" r:id="rId105" xr:uid="{5B16329D-C885-DE47-8B31-AD7F86361093}"/>
+    <hyperlink ref="H125" r:id="rId106" xr:uid="{CF11FA97-D4DE-1A40-BB61-CA4D6D9B8D3F}"/>
+    <hyperlink ref="H126" r:id="rId107" xr:uid="{8BE6396A-F4C0-1247-99E0-1404C6A0DF72}"/>
+    <hyperlink ref="H127" r:id="rId108" xr:uid="{9A07959C-AF40-3841-BD27-5AD7778E3998}"/>
+    <hyperlink ref="H128" r:id="rId109" xr:uid="{290330E5-1728-C14E-8013-F17872DF3FF2}"/>
+    <hyperlink ref="H129" r:id="rId110" xr:uid="{F82EF5D5-44E6-9C49-9DE4-BC54EE7717E3}"/>
+    <hyperlink ref="H130" r:id="rId111" xr:uid="{AD939B93-7714-F849-8429-A4470E1A6ED4}"/>
+    <hyperlink ref="H131" r:id="rId112" xr:uid="{C4982BA1-8F4D-1944-8C50-4D8132FCAB54}"/>
+    <hyperlink ref="H132" r:id="rId113" xr:uid="{503FBD7F-AAED-F842-8CF7-9789AC13C47B}"/>
+    <hyperlink ref="H133" r:id="rId114" xr:uid="{2D4E9B0C-A0ED-DE47-B871-82318D7049B0}"/>
+    <hyperlink ref="H134" r:id="rId115" xr:uid="{D0D33C0E-E236-9F4A-8F73-519EAE7A731B}"/>
+    <hyperlink ref="H135" r:id="rId116" xr:uid="{107E34A8-4B58-C541-8351-B46C92790825}"/>
+    <hyperlink ref="H136" r:id="rId117" xr:uid="{533EBA65-E723-EC45-BB53-F3EEB3DCB45F}"/>
+    <hyperlink ref="H137" r:id="rId118" xr:uid="{A568CC42-5374-0D47-B412-0CF1F4A21083}"/>
+    <hyperlink ref="H138" r:id="rId119" xr:uid="{7C775AA2-AB62-624F-824F-193827BAFF2C}"/>
+    <hyperlink ref="H139" r:id="rId120" xr:uid="{AB17F0E3-00A3-D349-BC72-A6D11177E398}"/>
+    <hyperlink ref="H140" r:id="rId121" xr:uid="{CC4281B7-E3D8-8E4E-9C4E-801880B87FD8}"/>
+    <hyperlink ref="H141" r:id="rId122" xr:uid="{6442D099-98A4-1A4E-849A-AD47B7FE9F5F}"/>
+    <hyperlink ref="H142" r:id="rId123" xr:uid="{BDEB6ED6-7F8D-BB4A-AA94-252F91D4DBD2}"/>
+    <hyperlink ref="H143" r:id="rId124" xr:uid="{2D1217FE-30EB-C942-A590-8EEBEA7FCFFE}"/>
+    <hyperlink ref="H144" r:id="rId125" xr:uid="{EE8E0022-75C7-B54C-A866-2D1FD55D5CAD}"/>
+    <hyperlink ref="H145" r:id="rId126" xr:uid="{AC97968A-7936-9C4A-B505-DC625B1C512C}"/>
+    <hyperlink ref="H146" r:id="rId127" xr:uid="{25A11007-B7C7-2E4E-865E-7D281FC1E586}"/>
+    <hyperlink ref="H147" r:id="rId128" xr:uid="{0DE6676D-C44D-8344-B345-FDE1BE9EEA69}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a/ЛСсайт/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E52298-3149-6C49-A045-21F62CDF33FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C425EECA-C72F-9B42-905A-7069AB69675E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="410">
   <si>
     <t>id</t>
   </si>
@@ -959,6 +959,297 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1775368601/tg-products/mh1sazndcavrnpsenrvi.jpg</t>
+  </si>
+  <si>
+    <t>Топ Prada</t>
+  </si>
+  <si>
+    <t>Материал лен</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763026/tg-products/m8qb0s8qhagfv3bcpqns.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763036/tg-products/r41epwwsyvmp3mym3eph.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763040/tg-products/gugnjtnjhbcl0aef8iid.jpg</t>
+  </si>
+  <si>
+    <t>Топ Valentino</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763044/tg-products/imdijs4na3plosmk0803.jpg</t>
+  </si>
+  <si>
+    <t>Топ Brunello Cucinelli</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763048/tg-products/uhipsomniygc5faomkb2.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763085/tg-products/gcs1h8i5r2ecrspclaby.jpg</t>
+  </si>
+  <si>
+    <t>Платье Loewe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763089/tg-products/yzulps0hh4byv6njgqfi.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763092/tg-products/rrv2uhbfhuvpzrdkavor.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763095/tg-products/ocy1ecnrcrl6k7xcfkpo.jpg</t>
+  </si>
+  <si>
+    <t>Материал хлопок с шелком</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763098/tg-products/a8hslst4ho6chxhyj4ba.jpg</t>
+  </si>
+  <si>
+    <t>Туфли Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763140/tg-products/xgiiy7vmgr04at64twg0.jpg</t>
+  </si>
+  <si>
+    <t>Кроссовки Dior Tech</t>
+  </si>
+  <si>
+    <t>Материал ткань кожа замша</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763143/tg-products/acrd9vwz4ebhvz5jgirk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763146/tg-products/rnfhnancq8xvyw444eew.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763149/tg-products/matf7uushjerkpih2pwo.jpg</t>
+  </si>
+  <si>
+    <t>Рубашка YSL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763152/tg-products/d0pfefntvf13fdl0jdaq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763242/tg-products/cnhdssnoty3ayfvqwvv3.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763245/tg-products/h3dbe1lpqo4zm71ir3uf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763249/tg-products/jq1nhdxk8xpqe3pmc75q.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763251/tg-products/qjhwbrf4pywpqph8bai8.jpg</t>
+  </si>
+  <si>
+    <t>Кроссовки Dior Saltwind</t>
+  </si>
+  <si>
+    <t>Материал ткань каучук</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763254/tg-products/blgwt086pzsxeqw2n7ag.jpg</t>
+  </si>
+  <si>
+    <t>Балетки Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763481/tg-products/zmxsg5jfoyspv1uf8lci.jpg</t>
+  </si>
+  <si>
+    <t>Кардиган Brunello</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763484/tg-products/vqwmgjgc38svyxbve28t.jpg</t>
+  </si>
+  <si>
+    <t>Босоножки Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763487/tg-products/pwpitd4igk7p8ocz0ssa.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763490/tg-products/ia51oo3cmd1mr5fltojy.jpg</t>
+  </si>
+  <si>
+    <t>золотой</t>
+  </si>
+  <si>
+    <t>Рубашка Brunello</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763492/tg-products/danlye1kcodlrrpxufcs.jpg</t>
+  </si>
+  <si>
+    <t>Материал каучук</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763722/tg-products/w36nxtaceyyxzj9oro84.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763725/tg-products/oh8w7gt8ls86dxneufdt.jpg</t>
+  </si>
+  <si>
+    <t>Куртка Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763728/tg-products/a9j61zcmohsczmwftjsr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763730/tg-products/zhkfeljrvzeamua84039.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763733/tg-products/lpuefinayucplx1tpgsx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763736/tg-products/gbrej0iab64ghosclsm7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763739/tg-products/pzmixnk4ox8rkqu5mnhs.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763742/tg-products/o5nxba7ttclloyteujhm.jpg</t>
+  </si>
+  <si>
+    <t>Джинсы Louis Vuitton</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763745/tg-products/a3axeuvwgq4wvzhxzfm8.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763748/tg-products/nb2f2vmfi1wuousvdaoj.jpg</t>
+  </si>
+  <si>
+    <t>Платье Valentino</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763842/tg-products/fahiyyl1lgltqdw7ykma.jpg</t>
+  </si>
+  <si>
+    <t>Пиджак Dior</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763844/tg-products/cbohcdkrjbmm59x9otjm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763847/tg-products/pnuo4qgrv8ifc2aeuaa4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763850/tg-products/fz00zgyzsttanpqqwlwk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763853/tg-products/wvgdebousrzv3h424hve.jpg</t>
+  </si>
+  <si>
+    <t>Кроссовки Chanel</t>
+  </si>
+  <si>
+    <t>Материал кожа замша</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763962/tg-products/mwyd13uavrbgawyclfza.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763964/tg-products/wqs1aihbr7ktlxcoz10i.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763967/tg-products/h6uar7nmbs7y6adrkhfb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763969/tg-products/xyyhktqcjno34sb1rjgt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778763972/tg-products/cnfkvi9ar7mnnwcg66zn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764082/tg-products/xtrof4r3khgttqn9pjtu.jpg</t>
+  </si>
+  <si>
+    <t>Кроссовки Celine</t>
+  </si>
+  <si>
+    <t>Материал замша ткань</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764085/tg-products/y5hmcemmblxfczpdh08m.jpg</t>
+  </si>
+  <si>
+    <t>Сандалии Chanel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764087/tg-products/ya7psbjhn7bflt5rj5af.jpg</t>
+  </si>
+  <si>
+    <t>Босоножки Loewe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764093/tg-products/yld2xn6oojny7j5oplhr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764095/tg-products/ylltmqoifsoywqcl3gjy.jpg</t>
+  </si>
+  <si>
+    <t>Мюли Loro Piana</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764220/tg-products/b5xemmyeazgtsgh90hjn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764223/tg-products/cilf0eehxffw3vlgfgux.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764226/tg-products/l5xpcrjauz0pyzlyqqkm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764229/tg-products/fj7shxpwdxoomp3bdwok.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764232/tg-products/u32vff99681yajgqebhb.jpg</t>
+  </si>
+  <si>
+    <t>Туфли Roger Vivier</t>
+  </si>
+  <si>
+    <t>Материал шелк кожа</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764321/tg-products/aihzqnjwlgs7gnthypoh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764324/tg-products/iduosu6qhpx5v9dr7wgt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764328/tg-products/clsqyah3le2kydsijwex.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764330/tg-products/ptoqyq4psjudz1ayh0vx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764442/tg-products/lxqqhxccrkrzpnwdlcvz.jpg</t>
+  </si>
+  <si>
+    <t>Платье Hermes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764444/tg-products/rkv3gmlt1zzlshlbrv7o.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764447/tg-products/wtlfok5gknkaesc5ll7n.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dlexrnrhe/image/upload/v1778764450/tg-products/ztfo507sbbbjlpc5hwxp.jpg</t>
+  </si>
+  <si>
+    <t>Brunello</t>
+  </si>
+  <si>
+    <t>Roger Vivier</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1593,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M297"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7321,6 +7612,3800 @@
       <c r="M147" s="10">
         <v>46117</v>
       </c>
+    </row>
+    <row r="148" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D148" s="8">
+        <v>16000</v>
+      </c>
+      <c r="E148" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J148" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K148" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L148" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M148" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D149" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J149" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K149" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L149" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M149" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D150" s="8">
+        <v>16000</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J150" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L150" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M150" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D151" s="8">
+        <v>16000</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="I151" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J151" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K151" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L151" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M151" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8">
+        <v>19000</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="I152" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J152" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L152" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M152" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D153" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="I153" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J153" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K153" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L153" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M153" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C154" t="s">
+        <v>121</v>
+      </c>
+      <c r="D154" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H154" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="I154" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J154" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K154" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L154" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M154" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8">
+        <v>54000</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J155" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K155" s="8"/>
+      <c r="L155" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="M155" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H156" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="I156" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J156" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L156" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M156" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J157" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L157" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M157" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H158" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="I158" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J158" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M158" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="I159" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J159" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M159" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D160" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H160" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I160" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J160" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K160" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L160" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M160" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D161" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J161" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K161" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M161" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D162" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J162" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M162" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D163" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H163" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J163" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K163" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M163" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D164" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J164" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K164" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M164" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D165" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J165" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K165" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M165" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D166" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="I166" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J166" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K166" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M166" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D167" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J167" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K167" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L167" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M167" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D168" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H168" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I168" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J168" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L168" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M168" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D169" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H169" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="I169" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J169" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M169" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D170" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F170" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H170" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="I170" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J170" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L170" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M170" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D171" s="8">
+        <v>20000</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H171" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="I171" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J171" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="L171" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M171" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D172" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="I172" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J172" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M172" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D173" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I173" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J173" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L173" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M173" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D174" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H174" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J174" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L174" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M174" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="I175" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J175" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K175" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M175" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D176" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H176" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="I176" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J176" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K176" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L176" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M176" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H177" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I177" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J177" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K177" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M177" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D178" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H178" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="I178" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J178" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K178" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L178" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M178" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D179" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H179" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="I179" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J179" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M179" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="8">
+        <v>18000</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H180" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J180" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K180" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M180" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D181" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H181" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="I181" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J181" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K181" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M181" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" s="8">
+        <v>26000</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I182" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J182" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K182" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M182" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D183" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H183" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="I183" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J183" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K183" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M183" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184" s="8">
+        <v>38000</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H184" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="I184" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J184" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K184" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M184" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185" s="8">
+        <v>18000</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H185" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="I185" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K185" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M185" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H186" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="I186" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J186" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K186" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M186" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H187" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="I187" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J187" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K187" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M187" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D188" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H188" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="I188" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J188" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K188" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L188" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M188" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D189" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H189" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="I189" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J189" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K189" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L189" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M189" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190" s="8">
+        <v>32000</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F190" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H190" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="I190" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J190" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K190" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M190" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D191" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H191" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="I191" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J191" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K191" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L191" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M191" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D192" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H192" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="I192" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J192" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K192" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M192" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D193" s="8">
+        <v>28000</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H193" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="I193" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J193" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K193" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L193" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M193" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D194" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H194" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="I194" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J194" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L194" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M194" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D195" s="8">
+        <v>28000</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H195" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="I195" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J195" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K195" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L195" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M195" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D196" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H196" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="I196" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J196" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K196" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L196" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M196" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D197" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H197" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="I197" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J197" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K197" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M197" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D198" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F198" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H198" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="I198" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K198" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M198" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D199" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H199" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="I199" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J199" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K199" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M199" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D200" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H200" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="I200" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K200" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L200" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M200" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D201" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H201" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="I201" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J201" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K201" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L201" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M201" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C202" t="s">
+        <v>121</v>
+      </c>
+      <c r="D202" s="8">
+        <v>22000</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H202" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="I202" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J202" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K202" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L202" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M202" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D203" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H203" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="I203" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J203" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K203" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L203" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M203" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D204" s="8">
+        <v>38000</v>
+      </c>
+      <c r="E204" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="I204" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J204" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K204" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M204" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D205" s="8">
+        <v>21000</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H205" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="I205" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J205" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K205" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M205" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D206" s="8">
+        <v>24000</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H206" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="I206" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J206" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K206" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L206" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M206" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207" s="8">
+        <v>12000</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H207" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="I207" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J207" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K207" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M207" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D208" s="8">
+        <v>38000</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H208" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="I208" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J208" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K208" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M208" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C209" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D209" s="8">
+        <v>27000</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="I209" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K209" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M209" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D210" s="8">
+        <v>30000</v>
+      </c>
+      <c r="E210" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H210" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="I210" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J210" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K210" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M210" s="10">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
+      <c r="D211" s="8"/>
+      <c r="E211" s="8"/>
+      <c r="F211" s="8"/>
+      <c r="G211" s="8"/>
+      <c r="H211" s="8"/>
+      <c r="I211" s="8"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="8"/>
+      <c r="L211" s="8"/>
+      <c r="M211" s="8"/>
+    </row>
+    <row r="212" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="8"/>
+      <c r="E212" s="8"/>
+      <c r="F212" s="8"/>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="8"/>
+      <c r="J212" s="8"/>
+      <c r="K212" s="8"/>
+      <c r="L212" s="8"/>
+      <c r="M212" s="8"/>
+    </row>
+    <row r="213" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="8"/>
+      <c r="E213" s="8"/>
+      <c r="F213" s="8"/>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="8"/>
+      <c r="J213" s="8"/>
+      <c r="K213" s="8"/>
+      <c r="L213" s="8"/>
+      <c r="M213" s="8"/>
+    </row>
+    <row r="214" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="8"/>
+      <c r="E214" s="8"/>
+      <c r="F214" s="8"/>
+      <c r="G214" s="8"/>
+      <c r="H214" s="8"/>
+      <c r="I214" s="8"/>
+      <c r="J214" s="8"/>
+      <c r="K214" s="8"/>
+      <c r="L214" s="8"/>
+      <c r="M214" s="8"/>
+    </row>
+    <row r="215" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="8"/>
+      <c r="E215" s="8"/>
+      <c r="F215" s="8"/>
+      <c r="G215" s="8"/>
+      <c r="H215" s="8"/>
+      <c r="I215" s="8"/>
+      <c r="J215" s="8"/>
+      <c r="K215" s="8"/>
+      <c r="L215" s="8"/>
+      <c r="M215" s="8"/>
+    </row>
+    <row r="216" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
+      <c r="D216" s="8"/>
+      <c r="E216" s="8"/>
+      <c r="F216" s="8"/>
+      <c r="G216" s="8"/>
+      <c r="H216" s="8"/>
+      <c r="I216" s="8"/>
+      <c r="J216" s="8"/>
+      <c r="K216" s="8"/>
+      <c r="L216" s="8"/>
+      <c r="M216" s="8"/>
+    </row>
+    <row r="217" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
+      <c r="D217" s="8"/>
+      <c r="E217" s="8"/>
+      <c r="F217" s="8"/>
+      <c r="G217" s="8"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="8"/>
+      <c r="J217" s="8"/>
+      <c r="K217" s="8"/>
+      <c r="L217" s="8"/>
+      <c r="M217" s="8"/>
+    </row>
+    <row r="218" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
+      <c r="D218" s="8"/>
+      <c r="E218" s="8"/>
+      <c r="F218" s="8"/>
+      <c r="G218" s="8"/>
+      <c r="H218" s="8"/>
+      <c r="I218" s="8"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="8"/>
+      <c r="L218" s="8"/>
+      <c r="M218" s="8"/>
+    </row>
+    <row r="219" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="8"/>
+      <c r="E219" s="8"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="8"/>
+      <c r="H219" s="8"/>
+      <c r="I219" s="8"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="8"/>
+      <c r="L219" s="8"/>
+      <c r="M219" s="8"/>
+    </row>
+    <row r="220" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="8"/>
+      <c r="E220" s="8"/>
+      <c r="F220" s="8"/>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="8"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="8"/>
+      <c r="L220" s="8"/>
+      <c r="M220" s="8"/>
+    </row>
+    <row r="221" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="8"/>
+      <c r="E221" s="8"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="8"/>
+      <c r="H221" s="8"/>
+      <c r="I221" s="8"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="8"/>
+      <c r="L221" s="8"/>
+      <c r="M221" s="8"/>
+    </row>
+    <row r="222" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="8"/>
+      <c r="E222" s="8"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="8"/>
+      <c r="H222" s="8"/>
+      <c r="I222" s="8"/>
+      <c r="J222" s="8"/>
+      <c r="K222" s="8"/>
+      <c r="L222" s="8"/>
+      <c r="M222" s="8"/>
+    </row>
+    <row r="223" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="8"/>
+      <c r="E223" s="8"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="8"/>
+      <c r="H223" s="8"/>
+      <c r="I223" s="8"/>
+      <c r="J223" s="8"/>
+      <c r="K223" s="8"/>
+      <c r="L223" s="8"/>
+      <c r="M223" s="8"/>
+    </row>
+    <row r="224" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="8"/>
+      <c r="E224" s="8"/>
+      <c r="F224" s="8"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="8"/>
+      <c r="J224" s="8"/>
+      <c r="K224" s="8"/>
+      <c r="L224" s="8"/>
+      <c r="M224" s="8"/>
+    </row>
+    <row r="225" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="8"/>
+      <c r="E225" s="8"/>
+      <c r="F225" s="8"/>
+      <c r="G225" s="8"/>
+      <c r="H225" s="8"/>
+      <c r="I225" s="8"/>
+      <c r="J225" s="8"/>
+      <c r="K225" s="8"/>
+      <c r="L225" s="8"/>
+      <c r="M225" s="8"/>
+    </row>
+    <row r="226" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="8"/>
+      <c r="E226" s="8"/>
+      <c r="F226" s="8"/>
+      <c r="G226" s="8"/>
+      <c r="H226" s="8"/>
+      <c r="I226" s="8"/>
+      <c r="J226" s="8"/>
+      <c r="K226" s="8"/>
+      <c r="L226" s="8"/>
+      <c r="M226" s="8"/>
+    </row>
+    <row r="227" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="8"/>
+      <c r="E227" s="8"/>
+      <c r="F227" s="8"/>
+      <c r="G227" s="8"/>
+      <c r="H227" s="8"/>
+      <c r="I227" s="8"/>
+      <c r="J227" s="8"/>
+      <c r="K227" s="8"/>
+      <c r="L227" s="8"/>
+      <c r="M227" s="8"/>
+    </row>
+    <row r="228" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="8"/>
+      <c r="E228" s="8"/>
+      <c r="F228" s="8"/>
+      <c r="G228" s="8"/>
+      <c r="H228" s="8"/>
+      <c r="I228" s="8"/>
+      <c r="J228" s="8"/>
+      <c r="K228" s="8"/>
+      <c r="L228" s="8"/>
+      <c r="M228" s="8"/>
+    </row>
+    <row r="229" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="8"/>
+      <c r="E229" s="8"/>
+      <c r="F229" s="8"/>
+      <c r="G229" s="8"/>
+      <c r="H229" s="8"/>
+      <c r="I229" s="8"/>
+      <c r="J229" s="8"/>
+      <c r="K229" s="8"/>
+      <c r="L229" s="8"/>
+      <c r="M229" s="8"/>
+    </row>
+    <row r="230" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="8"/>
+      <c r="E230" s="8"/>
+      <c r="F230" s="8"/>
+      <c r="G230" s="8"/>
+      <c r="H230" s="8"/>
+      <c r="I230" s="8"/>
+      <c r="J230" s="8"/>
+      <c r="K230" s="8"/>
+      <c r="L230" s="8"/>
+      <c r="M230" s="8"/>
+    </row>
+    <row r="231" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="8"/>
+      <c r="E231" s="8"/>
+      <c r="F231" s="8"/>
+      <c r="G231" s="8"/>
+      <c r="H231" s="8"/>
+      <c r="I231" s="8"/>
+      <c r="J231" s="8"/>
+      <c r="K231" s="8"/>
+      <c r="L231" s="8"/>
+      <c r="M231" s="8"/>
+    </row>
+    <row r="232" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="8"/>
+      <c r="E232" s="8"/>
+      <c r="F232" s="8"/>
+      <c r="G232" s="8"/>
+      <c r="H232" s="8"/>
+      <c r="I232" s="8"/>
+      <c r="J232" s="8"/>
+      <c r="K232" s="8"/>
+      <c r="L232" s="8"/>
+      <c r="M232" s="8"/>
+    </row>
+    <row r="233" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="8"/>
+      <c r="E233" s="8"/>
+      <c r="F233" s="8"/>
+      <c r="G233" s="8"/>
+      <c r="H233" s="8"/>
+      <c r="I233" s="8"/>
+      <c r="J233" s="8"/>
+      <c r="K233" s="8"/>
+      <c r="L233" s="8"/>
+      <c r="M233" s="8"/>
+    </row>
+    <row r="234" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B234" s="8"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="8"/>
+      <c r="E234" s="8"/>
+      <c r="F234" s="8"/>
+      <c r="G234" s="8"/>
+      <c r="H234" s="8"/>
+      <c r="I234" s="8"/>
+      <c r="J234" s="8"/>
+      <c r="K234" s="8"/>
+      <c r="L234" s="8"/>
+      <c r="M234" s="8"/>
+    </row>
+    <row r="235" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="8"/>
+      <c r="E235" s="8"/>
+      <c r="F235" s="8"/>
+      <c r="G235" s="8"/>
+      <c r="H235" s="8"/>
+      <c r="I235" s="8"/>
+      <c r="J235" s="8"/>
+      <c r="K235" s="8"/>
+      <c r="L235" s="8"/>
+      <c r="M235" s="8"/>
+    </row>
+    <row r="236" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="8"/>
+      <c r="E236" s="8"/>
+      <c r="F236" s="8"/>
+      <c r="G236" s="8"/>
+      <c r="H236" s="8"/>
+      <c r="I236" s="8"/>
+      <c r="J236" s="8"/>
+      <c r="K236" s="8"/>
+      <c r="L236" s="8"/>
+      <c r="M236" s="8"/>
+    </row>
+    <row r="237" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="8"/>
+      <c r="E237" s="8"/>
+      <c r="F237" s="8"/>
+      <c r="G237" s="8"/>
+      <c r="H237" s="8"/>
+      <c r="I237" s="8"/>
+      <c r="J237" s="8"/>
+      <c r="K237" s="8"/>
+      <c r="L237" s="8"/>
+      <c r="M237" s="8"/>
+    </row>
+    <row r="238" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="8"/>
+      <c r="E238" s="8"/>
+      <c r="F238" s="8"/>
+      <c r="G238" s="8"/>
+      <c r="H238" s="8"/>
+      <c r="I238" s="8"/>
+      <c r="J238" s="8"/>
+      <c r="K238" s="8"/>
+      <c r="L238" s="8"/>
+      <c r="M238" s="8"/>
+    </row>
+    <row r="239" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="8"/>
+      <c r="E239" s="8"/>
+      <c r="F239" s="8"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="8"/>
+      <c r="J239" s="8"/>
+      <c r="K239" s="8"/>
+      <c r="L239" s="8"/>
+      <c r="M239" s="8"/>
+    </row>
+    <row r="240" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="8"/>
+      <c r="E240" s="8"/>
+      <c r="F240" s="8"/>
+      <c r="G240" s="8"/>
+      <c r="H240" s="8"/>
+      <c r="I240" s="8"/>
+      <c r="J240" s="8"/>
+      <c r="K240" s="8"/>
+      <c r="L240" s="8"/>
+      <c r="M240" s="8"/>
+    </row>
+    <row r="241" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="8"/>
+      <c r="E241" s="8"/>
+      <c r="F241" s="8"/>
+      <c r="G241" s="8"/>
+      <c r="H241" s="8"/>
+      <c r="I241" s="8"/>
+      <c r="J241" s="8"/>
+      <c r="K241" s="8"/>
+      <c r="L241" s="8"/>
+      <c r="M241" s="8"/>
+    </row>
+    <row r="242" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="8"/>
+      <c r="E242" s="8"/>
+      <c r="F242" s="8"/>
+      <c r="G242" s="8"/>
+      <c r="H242" s="8"/>
+      <c r="I242" s="8"/>
+      <c r="J242" s="8"/>
+      <c r="K242" s="8"/>
+      <c r="L242" s="8"/>
+      <c r="M242" s="8"/>
+    </row>
+    <row r="243" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B243" s="8"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="8"/>
+      <c r="E243" s="8"/>
+      <c r="F243" s="8"/>
+      <c r="G243" s="8"/>
+      <c r="H243" s="8"/>
+      <c r="I243" s="8"/>
+      <c r="J243" s="8"/>
+      <c r="K243" s="8"/>
+      <c r="L243" s="8"/>
+      <c r="M243" s="8"/>
+    </row>
+    <row r="244" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="8"/>
+      <c r="E244" s="8"/>
+      <c r="F244" s="8"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="8"/>
+      <c r="J244" s="8"/>
+      <c r="K244" s="8"/>
+      <c r="L244" s="8"/>
+      <c r="M244" s="8"/>
+    </row>
+    <row r="245" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="8"/>
+      <c r="E245" s="8"/>
+      <c r="F245" s="8"/>
+      <c r="G245" s="8"/>
+      <c r="H245" s="8"/>
+      <c r="I245" s="8"/>
+      <c r="J245" s="8"/>
+      <c r="K245" s="8"/>
+      <c r="L245" s="8"/>
+      <c r="M245" s="8"/>
+    </row>
+    <row r="246" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="8"/>
+      <c r="E246" s="8"/>
+      <c r="F246" s="8"/>
+      <c r="G246" s="8"/>
+      <c r="H246" s="8"/>
+      <c r="I246" s="8"/>
+      <c r="J246" s="8"/>
+      <c r="K246" s="8"/>
+      <c r="L246" s="8"/>
+      <c r="M246" s="8"/>
+    </row>
+    <row r="247" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="8"/>
+      <c r="E247" s="8"/>
+      <c r="F247" s="8"/>
+      <c r="G247" s="8"/>
+      <c r="H247" s="8"/>
+      <c r="I247" s="8"/>
+      <c r="J247" s="8"/>
+      <c r="K247" s="8"/>
+      <c r="L247" s="8"/>
+      <c r="M247" s="8"/>
+    </row>
+    <row r="248" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="8"/>
+      <c r="E248" s="8"/>
+      <c r="F248" s="8"/>
+      <c r="G248" s="8"/>
+      <c r="H248" s="8"/>
+      <c r="I248" s="8"/>
+      <c r="J248" s="8"/>
+      <c r="K248" s="8"/>
+      <c r="L248" s="8"/>
+      <c r="M248" s="8"/>
+    </row>
+    <row r="249" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="8"/>
+      <c r="E249" s="8"/>
+      <c r="F249" s="8"/>
+      <c r="G249" s="8"/>
+      <c r="H249" s="8"/>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="8"/>
+      <c r="L249" s="8"/>
+      <c r="M249" s="8"/>
+    </row>
+    <row r="250" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="8"/>
+      <c r="E250" s="8"/>
+      <c r="F250" s="8"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="8"/>
+      <c r="L250" s="8"/>
+      <c r="M250" s="8"/>
+    </row>
+    <row r="251" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="8"/>
+      <c r="E251" s="8"/>
+      <c r="F251" s="8"/>
+      <c r="G251" s="8"/>
+      <c r="H251" s="8"/>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="8"/>
+      <c r="L251" s="8"/>
+      <c r="M251" s="8"/>
+    </row>
+    <row r="252" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="8"/>
+      <c r="E252" s="8"/>
+      <c r="F252" s="8"/>
+      <c r="G252" s="8"/>
+      <c r="H252" s="8"/>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="8"/>
+      <c r="L252" s="8"/>
+      <c r="M252" s="8"/>
+    </row>
+    <row r="253" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="8"/>
+      <c r="E253" s="8"/>
+      <c r="F253" s="8"/>
+      <c r="G253" s="8"/>
+      <c r="H253" s="8"/>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="8"/>
+      <c r="L253" s="8"/>
+      <c r="M253" s="8"/>
+    </row>
+    <row r="254" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="8"/>
+      <c r="E254" s="8"/>
+      <c r="F254" s="8"/>
+      <c r="G254" s="8"/>
+      <c r="H254" s="8"/>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="8"/>
+      <c r="L254" s="8"/>
+      <c r="M254" s="8"/>
+    </row>
+    <row r="255" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B255" s="8"/>
+      <c r="C255" s="8"/>
+      <c r="D255" s="8"/>
+      <c r="E255" s="8"/>
+      <c r="F255" s="8"/>
+      <c r="G255" s="8"/>
+      <c r="H255" s="8"/>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="8"/>
+      <c r="L255" s="8"/>
+      <c r="M255" s="8"/>
+    </row>
+    <row r="256" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B256" s="8"/>
+      <c r="C256" s="8"/>
+      <c r="D256" s="8"/>
+      <c r="E256" s="8"/>
+      <c r="F256" s="8"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="8"/>
+      <c r="L256" s="8"/>
+      <c r="M256" s="8"/>
+    </row>
+    <row r="257" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B257" s="8"/>
+      <c r="C257" s="8"/>
+      <c r="D257" s="8"/>
+      <c r="E257" s="8"/>
+      <c r="F257" s="8"/>
+      <c r="G257" s="8"/>
+      <c r="H257" s="8"/>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="8"/>
+      <c r="L257" s="8"/>
+      <c r="M257" s="8"/>
+    </row>
+    <row r="258" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="8"/>
+      <c r="E258" s="8"/>
+      <c r="F258" s="8"/>
+      <c r="G258" s="8"/>
+      <c r="H258" s="8"/>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="8"/>
+      <c r="L258" s="8"/>
+      <c r="M258" s="8"/>
+    </row>
+    <row r="259" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B259" s="8"/>
+      <c r="C259" s="8"/>
+      <c r="D259" s="8"/>
+      <c r="E259" s="8"/>
+      <c r="F259" s="8"/>
+      <c r="G259" s="8"/>
+      <c r="H259" s="8"/>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="8"/>
+      <c r="L259" s="8"/>
+      <c r="M259" s="8"/>
+    </row>
+    <row r="260" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B260" s="8"/>
+      <c r="C260" s="8"/>
+      <c r="D260" s="8"/>
+      <c r="E260" s="8"/>
+      <c r="F260" s="8"/>
+      <c r="G260" s="8"/>
+      <c r="H260" s="8"/>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="8"/>
+      <c r="L260" s="8"/>
+      <c r="M260" s="8"/>
+    </row>
+    <row r="261" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B261" s="8"/>
+      <c r="C261" s="8"/>
+      <c r="D261" s="8"/>
+      <c r="E261" s="8"/>
+      <c r="F261" s="8"/>
+      <c r="G261" s="8"/>
+      <c r="H261" s="8"/>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="8"/>
+      <c r="L261" s="8"/>
+      <c r="M261" s="8"/>
+    </row>
+    <row r="262" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B262" s="8"/>
+      <c r="C262" s="8"/>
+      <c r="D262" s="8"/>
+      <c r="E262" s="8"/>
+      <c r="F262" s="8"/>
+      <c r="G262" s="8"/>
+      <c r="H262" s="8"/>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="8"/>
+      <c r="L262" s="8"/>
+      <c r="M262" s="8"/>
+    </row>
+    <row r="263" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B263" s="8"/>
+      <c r="C263" s="8"/>
+      <c r="D263" s="8"/>
+      <c r="E263" s="8"/>
+      <c r="F263" s="8"/>
+      <c r="G263" s="8"/>
+      <c r="H263" s="8"/>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="8"/>
+      <c r="L263" s="8"/>
+      <c r="M263" s="8"/>
+    </row>
+    <row r="264" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B264" s="8"/>
+      <c r="C264" s="8"/>
+      <c r="D264" s="8"/>
+      <c r="E264" s="8"/>
+      <c r="F264" s="8"/>
+      <c r="G264" s="8"/>
+      <c r="H264" s="8"/>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="8"/>
+      <c r="L264" s="8"/>
+      <c r="M264" s="8"/>
+    </row>
+    <row r="265" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B265" s="8"/>
+      <c r="C265" s="8"/>
+      <c r="D265" s="8"/>
+      <c r="E265" s="8"/>
+      <c r="F265" s="8"/>
+      <c r="G265" s="8"/>
+      <c r="H265" s="8"/>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="8"/>
+      <c r="L265" s="8"/>
+      <c r="M265" s="8"/>
+    </row>
+    <row r="266" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B266" s="8"/>
+      <c r="C266" s="8"/>
+      <c r="D266" s="8"/>
+      <c r="E266" s="8"/>
+      <c r="F266" s="8"/>
+      <c r="G266" s="8"/>
+      <c r="H266" s="8"/>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="8"/>
+      <c r="L266" s="8"/>
+      <c r="M266" s="8"/>
+    </row>
+    <row r="267" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B267" s="8"/>
+      <c r="C267" s="8"/>
+      <c r="D267" s="8"/>
+      <c r="E267" s="8"/>
+      <c r="F267" s="8"/>
+      <c r="G267" s="8"/>
+      <c r="H267" s="8"/>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="8"/>
+      <c r="L267" s="8"/>
+      <c r="M267" s="8"/>
+    </row>
+    <row r="268" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B268" s="8"/>
+      <c r="C268" s="8"/>
+      <c r="D268" s="8"/>
+      <c r="E268" s="8"/>
+      <c r="F268" s="8"/>
+      <c r="G268" s="8"/>
+      <c r="H268" s="8"/>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="8"/>
+      <c r="L268" s="8"/>
+      <c r="M268" s="8"/>
+    </row>
+    <row r="269" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="8"/>
+      <c r="E269" s="8"/>
+      <c r="F269" s="8"/>
+      <c r="G269" s="8"/>
+      <c r="H269" s="8"/>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="8"/>
+      <c r="L269" s="8"/>
+      <c r="M269" s="8"/>
+    </row>
+    <row r="270" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="8"/>
+      <c r="E270" s="8"/>
+      <c r="F270" s="8"/>
+      <c r="G270" s="8"/>
+      <c r="H270" s="8"/>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="8"/>
+      <c r="L270" s="8"/>
+      <c r="M270" s="8"/>
+    </row>
+    <row r="271" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="8"/>
+      <c r="E271" s="8"/>
+      <c r="F271" s="8"/>
+      <c r="G271" s="8"/>
+      <c r="H271" s="8"/>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="8"/>
+      <c r="L271" s="8"/>
+      <c r="M271" s="8"/>
+    </row>
+    <row r="272" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="8"/>
+      <c r="E272" s="8"/>
+      <c r="F272" s="8"/>
+      <c r="G272" s="8"/>
+      <c r="H272" s="8"/>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="8"/>
+      <c r="L272" s="8"/>
+      <c r="M272" s="8"/>
+    </row>
+    <row r="273" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B273" s="8"/>
+      <c r="C273" s="8"/>
+      <c r="D273" s="8"/>
+      <c r="E273" s="8"/>
+      <c r="F273" s="8"/>
+      <c r="G273" s="8"/>
+      <c r="H273" s="8"/>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="8"/>
+      <c r="L273" s="8"/>
+      <c r="M273" s="8"/>
+    </row>
+    <row r="274" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B274" s="8"/>
+      <c r="C274" s="8"/>
+      <c r="D274" s="8"/>
+      <c r="E274" s="8"/>
+      <c r="F274" s="8"/>
+      <c r="G274" s="8"/>
+      <c r="H274" s="8"/>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="8"/>
+      <c r="L274" s="8"/>
+      <c r="M274" s="8"/>
+    </row>
+    <row r="275" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B275" s="8"/>
+      <c r="C275" s="8"/>
+      <c r="D275" s="8"/>
+      <c r="E275" s="8"/>
+      <c r="F275" s="8"/>
+      <c r="G275" s="8"/>
+      <c r="H275" s="8"/>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="8"/>
+      <c r="L275" s="8"/>
+      <c r="M275" s="8"/>
+    </row>
+    <row r="276" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B276" s="8"/>
+      <c r="C276" s="8"/>
+      <c r="D276" s="8"/>
+      <c r="E276" s="8"/>
+      <c r="F276" s="8"/>
+      <c r="G276" s="8"/>
+      <c r="H276" s="8"/>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="8"/>
+      <c r="L276" s="8"/>
+      <c r="M276" s="8"/>
+    </row>
+    <row r="277" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B277" s="8"/>
+      <c r="C277" s="8"/>
+      <c r="D277" s="8"/>
+      <c r="E277" s="8"/>
+      <c r="F277" s="8"/>
+      <c r="G277" s="8"/>
+      <c r="H277" s="8"/>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="8"/>
+      <c r="L277" s="8"/>
+      <c r="M277" s="8"/>
+    </row>
+    <row r="278" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B278" s="8"/>
+      <c r="C278" s="8"/>
+      <c r="D278" s="8"/>
+      <c r="E278" s="8"/>
+      <c r="F278" s="8"/>
+      <c r="G278" s="8"/>
+      <c r="H278" s="8"/>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="8"/>
+      <c r="L278" s="8"/>
+      <c r="M278" s="8"/>
+    </row>
+    <row r="279" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
+      <c r="D279" s="8"/>
+      <c r="E279" s="8"/>
+      <c r="F279" s="8"/>
+      <c r="G279" s="8"/>
+      <c r="H279" s="8"/>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="8"/>
+      <c r="L279" s="8"/>
+      <c r="M279" s="8"/>
+    </row>
+    <row r="280" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B280" s="8"/>
+      <c r="C280" s="8"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="8"/>
+      <c r="F280" s="8"/>
+      <c r="G280" s="8"/>
+      <c r="H280" s="8"/>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="8"/>
+      <c r="L280" s="8"/>
+      <c r="M280" s="8"/>
+    </row>
+    <row r="281" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B281" s="8"/>
+      <c r="C281" s="8"/>
+      <c r="D281" s="8"/>
+      <c r="E281" s="8"/>
+      <c r="F281" s="8"/>
+      <c r="G281" s="8"/>
+      <c r="H281" s="8"/>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="8"/>
+      <c r="L281" s="8"/>
+      <c r="M281" s="8"/>
+    </row>
+    <row r="282" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B282" s="8"/>
+      <c r="C282" s="8"/>
+      <c r="D282" s="8"/>
+      <c r="E282" s="8"/>
+      <c r="F282" s="8"/>
+      <c r="G282" s="8"/>
+      <c r="H282" s="8"/>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="8"/>
+      <c r="L282" s="8"/>
+      <c r="M282" s="8"/>
+    </row>
+    <row r="283" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B283" s="8"/>
+      <c r="C283" s="8"/>
+      <c r="D283" s="8"/>
+      <c r="E283" s="8"/>
+      <c r="F283" s="8"/>
+      <c r="G283" s="8"/>
+      <c r="H283" s="8"/>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="8"/>
+      <c r="L283" s="8"/>
+      <c r="M283" s="8"/>
+    </row>
+    <row r="284" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="8"/>
+      <c r="E284" s="8"/>
+      <c r="F284" s="8"/>
+      <c r="G284" s="8"/>
+      <c r="H284" s="8"/>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="8"/>
+      <c r="L284" s="8"/>
+      <c r="M284" s="8"/>
+    </row>
+    <row r="285" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B285" s="8"/>
+      <c r="C285" s="8"/>
+      <c r="D285" s="8"/>
+      <c r="E285" s="8"/>
+      <c r="F285" s="8"/>
+      <c r="G285" s="8"/>
+      <c r="H285" s="8"/>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="8"/>
+      <c r="L285" s="8"/>
+      <c r="M285" s="8"/>
+    </row>
+    <row r="286" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B286" s="8"/>
+      <c r="C286" s="8"/>
+      <c r="D286" s="8"/>
+      <c r="E286" s="8"/>
+      <c r="F286" s="8"/>
+      <c r="G286" s="8"/>
+      <c r="H286" s="8"/>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="8"/>
+      <c r="L286" s="8"/>
+      <c r="M286" s="8"/>
+    </row>
+    <row r="287" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
+      <c r="D287" s="8"/>
+      <c r="E287" s="8"/>
+      <c r="F287" s="8"/>
+      <c r="G287" s="8"/>
+      <c r="H287" s="8"/>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="8"/>
+      <c r="L287" s="8"/>
+      <c r="M287" s="8"/>
+    </row>
+    <row r="288" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B288" s="8"/>
+      <c r="C288" s="8"/>
+      <c r="D288" s="8"/>
+      <c r="E288" s="8"/>
+      <c r="F288" s="8"/>
+      <c r="G288" s="8"/>
+      <c r="H288" s="8"/>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="8"/>
+      <c r="L288" s="8"/>
+      <c r="M288" s="8"/>
+    </row>
+    <row r="289" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B289" s="8"/>
+      <c r="C289" s="8"/>
+      <c r="D289" s="8"/>
+      <c r="E289" s="8"/>
+      <c r="F289" s="8"/>
+      <c r="G289" s="8"/>
+      <c r="H289" s="8"/>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="8"/>
+      <c r="L289" s="8"/>
+      <c r="M289" s="8"/>
+    </row>
+    <row r="290" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B290" s="8"/>
+      <c r="C290" s="8"/>
+      <c r="D290" s="8"/>
+      <c r="E290" s="8"/>
+      <c r="F290" s="8"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="8"/>
+      <c r="L290" s="8"/>
+      <c r="M290" s="8"/>
+    </row>
+    <row r="291" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B291" s="8"/>
+      <c r="C291" s="8"/>
+      <c r="D291" s="8"/>
+      <c r="E291" s="8"/>
+      <c r="F291" s="8"/>
+      <c r="G291" s="8"/>
+      <c r="H291" s="8"/>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="8"/>
+      <c r="L291" s="8"/>
+      <c r="M291" s="8"/>
+    </row>
+    <row r="292" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B292" s="8"/>
+      <c r="C292" s="8"/>
+      <c r="D292" s="8"/>
+      <c r="E292" s="8"/>
+      <c r="F292" s="8"/>
+      <c r="G292" s="8"/>
+      <c r="H292" s="8"/>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="8"/>
+      <c r="L292" s="8"/>
+      <c r="M292" s="8"/>
+    </row>
+    <row r="293" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B293" s="8"/>
+      <c r="C293" s="8"/>
+      <c r="D293" s="8"/>
+      <c r="E293" s="8"/>
+      <c r="F293" s="8"/>
+      <c r="G293" s="8"/>
+      <c r="H293" s="8"/>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="8"/>
+      <c r="L293" s="8"/>
+      <c r="M293" s="8"/>
+    </row>
+    <row r="294" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B294" s="8"/>
+      <c r="C294" s="8"/>
+      <c r="D294" s="8"/>
+      <c r="E294" s="8"/>
+      <c r="F294" s="8"/>
+      <c r="G294" s="8"/>
+      <c r="H294" s="8"/>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="8"/>
+      <c r="L294" s="8"/>
+      <c r="M294" s="8"/>
+    </row>
+    <row r="295" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B295" s="8"/>
+      <c r="C295" s="8"/>
+      <c r="D295" s="8"/>
+      <c r="E295" s="8"/>
+      <c r="F295" s="8"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="8"/>
+      <c r="L295" s="8"/>
+      <c r="M295" s="8"/>
+    </row>
+    <row r="296" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B296" s="8"/>
+      <c r="C296" s="8"/>
+      <c r="D296" s="8"/>
+      <c r="E296" s="8"/>
+      <c r="F296" s="8"/>
+      <c r="G296" s="8"/>
+      <c r="H296" s="8"/>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="8"/>
+      <c r="L296" s="8"/>
+      <c r="M296" s="8"/>
+    </row>
+    <row r="297" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B297" s="8"/>
+      <c r="C297" s="8"/>
+      <c r="D297" s="8"/>
+      <c r="E297" s="8"/>
+      <c r="F297" s="8"/>
+      <c r="G297" s="8"/>
+      <c r="H297" s="8"/>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="8"/>
+      <c r="L297" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7452,6 +11537,69 @@
     <hyperlink ref="H145" r:id="rId126" xr:uid="{AC97968A-7936-9C4A-B505-DC625B1C512C}"/>
     <hyperlink ref="H146" r:id="rId127" xr:uid="{25A11007-B7C7-2E4E-865E-7D281FC1E586}"/>
     <hyperlink ref="H147" r:id="rId128" xr:uid="{0DE6676D-C44D-8344-B345-FDE1BE9EEA69}"/>
+    <hyperlink ref="H148" r:id="rId129" xr:uid="{EC9E0977-DF4A-AA4E-963A-EB8CAD60A4DC}"/>
+    <hyperlink ref="H149" r:id="rId130" xr:uid="{5AADB371-8FFD-0B4A-B873-E4C484693B82}"/>
+    <hyperlink ref="H150" r:id="rId131" xr:uid="{8C474EB9-3F8F-BC48-AB59-316FB6BB0E25}"/>
+    <hyperlink ref="H151" r:id="rId132" xr:uid="{8E248AA5-9DBD-1D42-B4DD-B9D861430AE1}"/>
+    <hyperlink ref="H152" r:id="rId133" xr:uid="{F7D70A82-34AE-AF47-BCC7-6D6878B21CCE}"/>
+    <hyperlink ref="H153" r:id="rId134" xr:uid="{28653D02-E019-AE40-B8B9-648141310F3E}"/>
+    <hyperlink ref="H154" r:id="rId135" xr:uid="{2BD2DEE6-DFBB-434F-A237-8526C72E1F77}"/>
+    <hyperlink ref="H155" r:id="rId136" xr:uid="{5DB828C0-5554-E64D-A70B-9CA1FA3F15BF}"/>
+    <hyperlink ref="H156" r:id="rId137" xr:uid="{C53E4FAA-97D8-CE4A-BA2E-79FAA498D500}"/>
+    <hyperlink ref="H157" r:id="rId138" xr:uid="{52262578-F12F-1E49-9937-E217CD05CDE1}"/>
+    <hyperlink ref="H158" r:id="rId139" xr:uid="{FA871E93-9ABF-5E4F-8715-136E08484073}"/>
+    <hyperlink ref="H159" r:id="rId140" xr:uid="{B5CE422D-0CB8-B946-AD1F-3E0354BBC088}"/>
+    <hyperlink ref="H160" r:id="rId141" xr:uid="{AEBA0BD8-1D89-4E41-931C-E0AF84924ADF}"/>
+    <hyperlink ref="H161" r:id="rId142" xr:uid="{8AC23FC2-1650-0643-A20F-48179440ACAD}"/>
+    <hyperlink ref="H162" r:id="rId143" xr:uid="{9FB94CB2-E11E-BA45-9D62-E41A8BB9203F}"/>
+    <hyperlink ref="H163" r:id="rId144" xr:uid="{E341C414-D1F4-E84B-8124-B9872336F949}"/>
+    <hyperlink ref="H164" r:id="rId145" xr:uid="{08C404B6-A842-7847-8F05-57390AB10F20}"/>
+    <hyperlink ref="H165" r:id="rId146" xr:uid="{A7C5A52B-C4CE-B543-B4C2-05CBCD078E5F}"/>
+    <hyperlink ref="H166" r:id="rId147" xr:uid="{1D2E1DC2-D74C-E24A-BD4E-58F810C245B1}"/>
+    <hyperlink ref="H167" r:id="rId148" xr:uid="{7DC154CA-1436-7D40-AD58-2262E1E93F0B}"/>
+    <hyperlink ref="H168" r:id="rId149" xr:uid="{02E1C972-96A5-D542-A0BB-9715F9A52E41}"/>
+    <hyperlink ref="H169" r:id="rId150" xr:uid="{82FD40D6-F139-CB4A-8DC8-3AEBA37D65A7}"/>
+    <hyperlink ref="H170" r:id="rId151" xr:uid="{21F6D3CC-D9BB-1646-9681-0DB4AA7D38CA}"/>
+    <hyperlink ref="H171" r:id="rId152" xr:uid="{58D1AE4B-1EB2-DD47-A422-22C3387145CC}"/>
+    <hyperlink ref="H172" r:id="rId153" xr:uid="{40FCC61C-FE10-3542-B9F9-988B1FA5BA34}"/>
+    <hyperlink ref="H173" r:id="rId154" xr:uid="{F98E04DD-D9EE-6E41-9621-335AD72DCFCE}"/>
+    <hyperlink ref="H174" r:id="rId155" xr:uid="{C39F7E65-3BA5-7E48-8F22-C72219F8C687}"/>
+    <hyperlink ref="H175" r:id="rId156" xr:uid="{D0D3AFEE-6DB4-214E-A194-4FE57E8F95DC}"/>
+    <hyperlink ref="H176" r:id="rId157" xr:uid="{E3B12125-D1F1-314E-9A2A-12F2B91837AE}"/>
+    <hyperlink ref="H177" r:id="rId158" xr:uid="{D04FD2B5-9F01-D645-A638-97B90789EE8A}"/>
+    <hyperlink ref="H178" r:id="rId159" xr:uid="{B0F2664A-3CC3-2049-AF14-68D894E5DEA2}"/>
+    <hyperlink ref="H179" r:id="rId160" xr:uid="{CE21B461-F272-C74B-B5E5-791BCE16ED91}"/>
+    <hyperlink ref="H180" r:id="rId161" xr:uid="{6FA4C398-5A99-8B49-B72E-7E765B389141}"/>
+    <hyperlink ref="H181" r:id="rId162" xr:uid="{75413CEE-8B14-8746-BA3A-9AC5A093FB80}"/>
+    <hyperlink ref="H182" r:id="rId163" xr:uid="{F3778B4F-B323-FB4E-BE6A-90E75CAE5873}"/>
+    <hyperlink ref="H183" r:id="rId164" xr:uid="{C9F0BAC5-BDDD-FC49-8811-6F817EF498E1}"/>
+    <hyperlink ref="H184" r:id="rId165" xr:uid="{5FAC5B2B-5903-8543-8736-892935941727}"/>
+    <hyperlink ref="H185" r:id="rId166" xr:uid="{D0109140-C48F-F94A-8D74-1013B5375A5C}"/>
+    <hyperlink ref="H186" r:id="rId167" xr:uid="{67B5DB8A-6363-2642-B234-08A00BB60128}"/>
+    <hyperlink ref="H187" r:id="rId168" xr:uid="{CA4F608F-863D-1D44-9D9C-52C4E9CBCD63}"/>
+    <hyperlink ref="H188" r:id="rId169" xr:uid="{9E730A28-83C5-BA4F-9DC4-D7CF7694B4FB}"/>
+    <hyperlink ref="H189" r:id="rId170" xr:uid="{FBE10143-F6D1-BD4F-BABE-5634E90F8343}"/>
+    <hyperlink ref="H190" r:id="rId171" xr:uid="{9ACEA381-3A10-F04A-97E9-CBC2B9D15536}"/>
+    <hyperlink ref="H191" r:id="rId172" xr:uid="{F314AEF8-D690-3447-AABB-CE2693F78511}"/>
+    <hyperlink ref="H192" r:id="rId173" xr:uid="{64448745-E95E-0D41-B07B-75420872CEDC}"/>
+    <hyperlink ref="H193" r:id="rId174" xr:uid="{59B0BB9B-0D39-0942-A665-34F9E65CBD3A}"/>
+    <hyperlink ref="H194" r:id="rId175" xr:uid="{04AE13F8-0A65-B342-89FC-2F850B34BEBA}"/>
+    <hyperlink ref="H195" r:id="rId176" xr:uid="{CC7DB67C-743C-B747-BA33-1BD75CC787AC}"/>
+    <hyperlink ref="H196" r:id="rId177" xr:uid="{52956D3C-5395-D44F-980A-2022CA2B68F9}"/>
+    <hyperlink ref="H197" r:id="rId178" xr:uid="{6254F2B3-2B69-A249-8D43-3E9CD99B58E5}"/>
+    <hyperlink ref="H198" r:id="rId179" xr:uid="{2215CDE7-318E-7A48-B42D-7E6BED58D7C5}"/>
+    <hyperlink ref="H199" r:id="rId180" xr:uid="{8F2FC8B2-E9CA-4544-9E23-FA273B4C5693}"/>
+    <hyperlink ref="H200" r:id="rId181" xr:uid="{696471E0-48CB-964C-BDEA-2304F7C49F89}"/>
+    <hyperlink ref="H201" r:id="rId182" xr:uid="{59835F94-55B2-4049-8C4C-A1FE410DBB43}"/>
+    <hyperlink ref="H202" r:id="rId183" xr:uid="{F9513D72-33FD-CD4F-B428-0038C84EB132}"/>
+    <hyperlink ref="H203" r:id="rId184" xr:uid="{2D1879A3-8033-A648-B31C-C4877C797A58}"/>
+    <hyperlink ref="H204" r:id="rId185" xr:uid="{40A1037A-69F9-A84D-8C91-5F8F4E07AC63}"/>
+    <hyperlink ref="H205" r:id="rId186" xr:uid="{3A51AF0A-4C73-4144-9922-08480E8B046A}"/>
+    <hyperlink ref="H206" r:id="rId187" xr:uid="{9D0B28B0-DA22-774B-8EFB-6B27F151F64D}"/>
+    <hyperlink ref="H207" r:id="rId188" xr:uid="{A9DA3372-A766-A845-AD52-6374AD0A5FE5}"/>
+    <hyperlink ref="H208" r:id="rId189" xr:uid="{3AB32D82-DC97-B84D-A2B3-69FDA9CC9FB6}"/>
+    <hyperlink ref="H209" r:id="rId190" xr:uid="{A8D6A4F9-1A73-6448-AF93-EDEA201EE988}"/>
+    <hyperlink ref="H210" r:id="rId191" xr:uid="{D57742F9-296D-EB48-AEFB-13EF9D5121E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
